--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1294,7 +1294,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>PU Staff Current Year - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2541,7 +2541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>PU Non Staff Current Year - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3791,7 +3791,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>PU Previous Year Comparison - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6999,7 +6999,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - JUL 2026 | uploaded 2026-08-17T11:13:04+05:30</t>
+          <t>Demand Previous Year Comparison - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -619,30 +619,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>232,594
-Cr. 23.26</t>
+          <t>236,563
+Cr. 23.66</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>-7,437
-Cr. -0.74</t>
+          <t>-3,468
+Cr. -0.35</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>408,928
-Cr. 40.89</t>
+          <t>404,959
+Cr. 40.50</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -671,14 +671,14 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,467,818
-Cr. 146.78</t>
+          <t>1,473,830
+Cr. 147.38</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>289,834
-Cr. 28.98</t>
+          <t>295,846
+Cr. 29.58</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -688,8 +688,8 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>2,141,084
-Cr. 214.11</t>
+          <t>2,135,072
+Cr. 213.51</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -775,30 +775,30 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>722,606
-Cr. 72.26</t>
+          <t>765,059
+Cr. 76.51</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>308,646
-Cr. 30.86</t>
+          <t>351,099
+Cr. 35.11</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>630,975
-Cr. 63.10</t>
+          <t>588,522
+Cr. 58.85</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -827,30 +827,30 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>800,112
-Cr. 80.01</t>
+          <t>838,163
+Cr. 83.82</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>105,972
-Cr. 10.60</t>
+          <t>144,023
+Cr. 14.40</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,259,838
-Cr. 125.98</t>
+          <t>1,221,787
+Cr. 122.18</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -879,30 +879,30 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,562,963
-Cr. 156.30</t>
+          <t>1,617,389
+Cr. 161.74</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>345,691
-Cr. 34.57</t>
+          <t>400,117
+Cr. 40.01</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,789,603
-Cr. 178.96</t>
+          <t>1,735,177
+Cr. 173.52</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -931,14 +931,14 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1,777,301
-Cr. 177.73</t>
+          <t>1,782,151
+Cr. 178.22</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>266,110
-Cr. 26.61</t>
+          <t>270,960
+Cr. 27.10</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -948,8 +948,8 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,651,465
-Cr. 265.15</t>
+          <t>2,646,615
+Cr. 264.66</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -983,30 +983,30 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3,545,214
-Cr. 354.52</t>
+          <t>4,605,644
+Cr. 460.56</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>-317,091
-Cr. -31.71</t>
+          <t>743,339
+Cr. 74.33</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>8,061,992
-Cr. 806.20</t>
+          <t>7,001,562
+Cr. 700.16</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -1035,14 +1035,14 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>807,750
-Cr. 80.78</t>
+          <t>810,746
+Cr. 81.07</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>209,076
-Cr. 20.91</t>
+          <t>212,072
+Cr. 21.21</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1052,8 +1052,8 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>585,082
-Cr. 58.51</t>
+          <t>582,086
+Cr. 58.21</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1087,25 +1087,25 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>355,866
-Cr. 35.59</t>
+          <t>356,768
+Cr. 35.68</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>30,178
-Cr. 3.02</t>
+          <t>31,080
+Cr. 3.11</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>638,772
-Cr. 63.88</t>
+          <t>637,870
+Cr. 63.79</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1187,30 +1187,30 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>12,479,934
-Cr. 1247.99</t>
+          <t>13,694,023
+Cr. 1369.40</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1,126,378
-Cr. 112.64</t>
+          <t>2,340,467
+Cr. 234.05</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>20,115,939
-Cr. 2011.59</t>
+          <t>18,901,850
+Cr. 1890.18</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -1239,14 +1239,14 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,569,032
-Cr. 156.90</t>
+          <t>1,569,443
+Cr. 156.94</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>206,233
-Cr. 20.62</t>
+          <t>206,644
+Cr. 20.66</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1256,13 +1256,13 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,582,077
-Cr. -158.21</t>
+          <t>-1,582,488
+Cr. -158.25</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12028</t>
+          <t>-12031</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>PU Staff Current Year - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2,454,892
-Cr. 245.49</t>
+          <t>2,453,873
+Cr. 245.39</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>205,828
-Cr. 20.58</t>
+          <t>204,809
+Cr. 20.48</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1422,8 +1422,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>4,251,517
-Cr. 425.15</t>
+          <t>4,252,536
+Cr. 425.25</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,579,845
-Cr. 157.98</t>
+          <t>1,579,536
+Cr. 157.95</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>220,441
-Cr. 22.04</t>
+          <t>220,132
+Cr. 22.01</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1469,8 +1469,8 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,520,608
-Cr. 252.06</t>
+          <t>2,520,917
+Cr. 252.09</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>269,991
-Cr. 27.00</t>
+          <t>269,887
+Cr. 26.99</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1,139
-Cr. 0.11</t>
+          <t>1,035
+Cr. 0.10</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1563,8 +1563,8 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>506,207
-Cr. 50.62</t>
+          <t>506,311
+Cr. 50.63</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1593,13 +1593,13 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>173,507
+          <t>173,467
 Cr. 17.35</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6,195
+          <t>6,155
 Cr. 0.62</t>
         </is>
       </c>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>323,102
+          <t>323,142
 Cr. 32.31</t>
         </is>
       </c>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>54,545
-Cr. 5.45</t>
+          <t>54,782
+Cr. 5.48</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>27,621
-Cr. 2.76</t>
+          <t>27,858
+Cr. 2.79</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1751,8 +1751,8 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>22,755
-Cr. 2.28</t>
+          <t>22,518
+Cr. 2.25</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1828,13 +1828,13 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>250,793
-Cr. 25.08</t>
+          <t>250,736
+Cr. 25.07</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-22,684
+          <t>-22,741
 Cr. -2.27</t>
         </is>
       </c>
@@ -1845,8 +1845,8 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>277,039
-Cr. 27.70</t>
+          <t>277,096
+Cr. 27.71</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -2063,30 +2063,30 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>10,194
-Cr. 1.02</t>
+          <t>10,103
+Cr. 1.01</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>4,801
-Cr. 0.48</t>
+          <t>4,710
+Cr. 0.47</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>8,429
-Cr. 0.84</t>
+          <t>8,520
+Cr. 0.85</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -2157,30 +2157,30 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>124,790
-Cr. 12.48</t>
+          <t>125,964
+Cr. 12.60</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>-425
-Cr. -0.04</t>
+          <t>749
+Cr. 0.07</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>259,602
-Cr. 25.96</t>
+          <t>258,428
+Cr. 25.84</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>6,509,817
-Cr. 650.98</t>
+          <t>6,509,608
+Cr. 650.96</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>882,069
-Cr. 88.21</t>
+          <t>881,860
+Cr. 88.19</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2503,8 +2503,8 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>9,797,703
-Cr. 979.77</t>
+          <t>9,797,912
+Cr. 979.79</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -2541,7 +2541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>PU Non Staff Current Year - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2746,30 +2746,30 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>521
-Cr. 0.05</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-471
-Cr. -0.05</t>
+          <t>-992
+Cr. -0.10</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2,779
-Cr. 0.28</t>
+          <t>3,300
+Cr. 0.33</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2934,30 +2934,30 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>588,317
-Cr. 58.83</t>
+          <t>737,391
+Cr. 73.74</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>237,595
-Cr. 23.76</t>
+          <t>386,669
+Cr. 38.67</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>480,435
-Cr. 48.04</t>
+          <t>331,361
+Cr. 33.14</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -2981,14 +2981,14 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>63,019
-Cr. 6.30</t>
+          <t>63,087
+Cr. 6.31</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>10,300
-Cr. 1.03</t>
+          <t>10,368
+Cr. 1.04</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>86,928
+          <t>86,860
 Cr. 8.69</t>
         </is>
       </c>
@@ -3028,30 +3028,30 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1,100,220
-Cr. 110.02</t>
+          <t>1,415,221
+Cr. 141.52</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>-230,054
-Cr. -23.01</t>
+          <t>84,947
+Cr. 8.49</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2,778,504
-Cr. 277.85</t>
+          <t>2,463,503
+Cr. 246.35</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -3075,30 +3075,30 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>23,900
-Cr. 2.39</t>
+          <t>65,407
+Cr. 6.54</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-7,259
-Cr. -0.73</t>
+          <t>34,248
+Cr. 3.42</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>71,373
-Cr. 7.14</t>
+          <t>29,866
+Cr. 2.99</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -3122,30 +3122,30 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1,658,467
-Cr. 165.85</t>
+          <t>1,686,250
+Cr. 168.62</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>262,139
-Cr. 26.21</t>
+          <t>289,922
+Cr. 28.99</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1,595,843
-Cr. 159.58</t>
+          <t>1,568,060
+Cr. 156.81</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -3169,30 +3169,30 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>534,261
-Cr. 53.43</t>
+          <t>692,235
+Cr. 69.22</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-343,089
-Cr. -34.31</t>
+          <t>-185,115
+Cr. -18.51</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2,091,179
-Cr. 209.12</t>
+          <t>1,933,205
+Cr. 193.32</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -3216,30 +3216,30 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>11,736
-Cr. 1.17</t>
+          <t>17,414
+Cr. 1.74</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-37,572
-Cr. -3.76</t>
+          <t>-31,894
+Cr. -3.19</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>143,812
-Cr. 14.38</t>
+          <t>138,134
+Cr. 13.81</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3263,30 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>30,820
-Cr. 3.08</t>
+          <t>44,460
+Cr. 4.45</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>-880
-Cr. -0.09</t>
+          <t>12,760
+Cr. 1.28</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>65,009
-Cr. 6.50</t>
+          <t>51,369
+Cr. 5.14</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -3404,30 +3404,30 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>1,807,074
-Cr. 180.71</t>
+          <t>2,303,206
+Cr. 230.32</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>268,642
-Cr. 26.86</t>
+          <t>764,774
+Cr. 76.48</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2,896,282
-Cr. 289.63</t>
+          <t>2,400,150
+Cr. 240.01</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -3451,30 +3451,30 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>32,191
-Cr. 3.22</t>
+          <t>32,998
+Cr. 3.30</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>25,336
-Cr. 2.53</t>
+          <t>26,143
+Cr. 2.61</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>481</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>138
-Cr. 0.01</t>
+          <t>-669
+Cr. -0.07</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -3498,30 +3498,30 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>32,191
-Cr. 3.22</t>
+          <t>32,998
+Cr. 3.30</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>25,403
-Cr. 2.54</t>
+          <t>26,210
+Cr. 2.62</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>486</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-259
-Cr. -0.03</t>
+          <t>-1,066
+Cr. -0.11</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -3592,25 +3592,25 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>36,812
+          <t>36,849
 Cr. 3.68</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>32,064
+          <t>32,101
 Cr. 3.21</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>776</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-10,714
-Cr. -1.07</t>
+          <t>-10,751
+Cr. -1.08</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3639,30 +3639,30 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>-466,261
-Cr. -46.63</t>
+          <t>-481,300
+Cr. -48.13</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>-438,279
-Cr. -43.83</t>
+          <t>-453,318
+Cr. -45.33</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>-1,186,560
-Cr. -118.66</t>
+          <t>-1,171,521
+Cr. -117.15</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -3686,30 +3686,30 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2,079,500
-Cr. 207.95</t>
+          <t>2,101,259
+Cr. 210.13</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>643,563
-Cr. 64.36</t>
+          <t>665,322
+Cr. 66.53</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-281,921
-Cr. -28.19</t>
+          <t>-303,680
+Cr. -30.37</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -3733,30 +3733,30 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>7,539,150
-Cr. 753.91</t>
+          <t>8,753,857
+Cr. 875.39</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>450,543
-Cr. 45.05</t>
+          <t>1,665,250
+Cr. 166.53</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>8,736,158
-Cr. 873.62</t>
+          <t>7,521,451
+Cr. 752.15</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -3784,14 +3784,14 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>PU Previous Year Comparison - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2,454,892
-Cr. 245.49</t>
+          <t>2,453,873
+Cr. 245.39</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>219,422
-Cr. 21.94</t>
+          <t>218,403
+Cr. 21.84</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3967,8 +3967,8 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>30,246
-Cr. 3.02</t>
+          <t>29,227
+Cr. 2.92</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1,579,845
-Cr. 157.98</t>
+          <t>1,579,536
+Cr. 157.95</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>213,027
-Cr. 21.30</t>
+          <t>212,718
+Cr. 21.27</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -4032,8 +4032,8 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>143,966
-Cr. 14.40</t>
+          <t>143,657
+Cr. 14.37</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>269,990
-Cr. 27.00</t>
+          <t>269,887
+Cr. 26.99</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>11,257
-Cr. 1.13</t>
+          <t>11,154
+Cr. 1.12</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -4162,8 +4162,8 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>5,618
-Cr. 0.56</t>
+          <t>5,515
+Cr. 0.55</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -4210,1877 +4210,1877 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>173,507
+          <t>173,467
 Cr. 17.35</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>7,931
+Cr. 0.79</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>5,627
+Cr. 0.56</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>PU - 08 - NPS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1,100,183
+Cr. 110.02</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>366,728
+Cr. 36.67</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>399,406
+Cr. 39.94</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>1,285,187
+Cr. 128.52</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>428,396
+Cr. 42.84</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>425,235
+Cr. 42.52</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>-3,161
+Cr. -0.32</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25,829
+Cr. 2.58</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PU - 10 - KMA</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>765,522
+Cr. 76.55</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>255,174
+Cr. 25.52</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>261,222
+Cr. 26.12</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>680,197
+Cr. 68.02</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>226,732
+Cr. 22.67</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>290,482
+Cr. 29.05</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>63,750
+Cr. 6.37</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>29,260
+Cr. 2.93</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>PU - 11 - OT</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>96,309
+Cr. 9.63</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>32,103
+Cr. 3.21</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>62,375
+Cr. 6.24</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>77,300
+Cr. 7.73</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>25,767
+Cr. 2.58</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>54,782
+Cr. 5.48</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>29,015
+Cr. 2.90</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>-7,593
+Cr. -0.76</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PU - 12 - NDA</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>280,806
+Cr. 28.08</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>93,602
+Cr. 9.36</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>93,733
+Cr. 9.37</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>209,913
+Cr. 20.99</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>69,971
+Cr. 7.00</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>98,022
+Cr. 9.80</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>28,051
+Cr. 2.81</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>4,289
+Cr. 0.43</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>PU - 13 - OA</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>551,574
+Cr. 55.16</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>183,858
+Cr. 18.39</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>253,677
+Cr. 25.37</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>527,832
+Cr. 52.78</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>175,944
+Cr. 17.59</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>250,736
+Cr. 25.07</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>74,792
+Cr. 7.48</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>-2,941
+Cr. -0.29</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>PU - 14 - FEES &amp; HON.</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>4,686
+Cr. 0.47</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1,562
+Cr. 0.16</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>322
+Cr. 0.03</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>3,566
+Cr. 0.36</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>1,189
+Cr. 0.12</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>380
+Cr. 0.04</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>-809
+Cr. -0.08</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>58
+Cr. 0.01</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>PU - 15 - TA</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>19,866
+Cr. 1.99</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>6,622
+Cr. 0.66</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>10,277
+Cr. 1.03</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>16,048
+Cr. 1.60</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>5,349
+Cr. 0.53</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>9,177
+Cr. 0.92</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>3,828
+Cr. 0.38</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>-1,100
+Cr. -0.11</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>PU - 16 - TE</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>523,466
+Cr. 52.35</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>174,489
+Cr. 17.45</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>165,458
+Cr. 16.55</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>308,081
+Cr. 30.81</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>102,694
+Cr. 10.27</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>176,121
+Cr. 17.61</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>73,427
+Cr. 7.34</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>10,663
+Cr. 1.07</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>PU - 17 - ATPP</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2,260
+Cr. 0.23</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>753
+Cr. 0.08</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2,110
+Cr. 0.21</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>703
+Cr. 0.07</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>-703
+Cr. -0.07</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>PU - 18 - OE</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>8,037
+Cr. 0.80</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2,679
+Cr. 0.27</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>8,252
+Cr. 0.83</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>2,751
+Cr. 0.28</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>-2,751
+Cr. -0.28</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>PU - 19 - Phone</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>606
+Cr. 0.06</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>202
+Cr. 0.02</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>655
+Cr. 0.07</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>218
+Cr. 0.02</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>-218
+Cr. -0.02</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>PU - 20 - Leave Salary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>14,388
+Cr. 1.44</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>4,796
+Cr. 0.48</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>5,170
+Cr. 0.52</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>18,623
+Cr. 1.86</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>6,208
+Cr. 0.62</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>10,103
+Cr. 1.01</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>3,895
+Cr. 0.39</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>4,933
+Cr. 0.49</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>PU - 21 - Adv Expenses</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2,848
+Cr. 0.28</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>949
+Cr. 0.09</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>3,300
+Cr. 0.33</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>1,100
+Cr. 0.11</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>-1,100
+Cr. -0.11</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>PU - 22 - Util(excl. elec.)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>PU - 23 - Rental Office Equip</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>40
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>13
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>42
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>14
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>-14
+Cr. -0.00</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PU - 24 - Printing and Stnry</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>12
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>4
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>215
+Cr. 0.02</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>72
+Cr. 0.01</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>-72
+Cr. -0.01</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>PU - 25 - Children Edu. Allow</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>364,718
+Cr. 36.47</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>121,573
+Cr. 12.16</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>354,718
+Cr. 35.47</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>379,418
+Cr. 37.94</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>126,473
+Cr. 12.65</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>358,456
+Cr. 35.85</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>231,983
+Cr. 23.20</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>3,738
+Cr. 0.37</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PU - 26 - Medical Expenses</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>321,438
+Cr. 32.14</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>107,146
+Cr. 10.71</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>142,245
+Cr. 14.22</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>384,392
+Cr. 38.44</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>128,131
+Cr. 12.81</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>125,963
+Cr. 12.60</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>-2,168
+Cr. -0.22</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>-16,282
+Cr. -1.63</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>PU - 27 - Materials from stock</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>1,445,603
+Cr. 144.56</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>481,868
+Cr. 48.19</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>376,832
+Cr. 37.68</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>1,068,752
+Cr. 106.88</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>356,251
+Cr. 35.63</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>737,390
+Cr. 73.74</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>381,139
+Cr. 38.11</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>360,558
+Cr. 36.06</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>PU - 28 - Materials-Dir. purchase</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>223,635
+Cr. 22.36</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>74,545
+Cr. 7.45</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>66,042
+Cr. 6.60</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>149,947
+Cr. 14.99</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>49,982
+Cr. 5.00</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>63,087
+Cr. 6.31</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>13,105
+Cr. 1.31</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>-2,955
+Cr. -0.30</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>PU - 29 - Remu. Re-engaged Staff</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>4
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>321
+Cr. 0.03</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>321
+Cr. 0.03</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>317
+Cr. 0.03</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>PU - 30 - Cost Of Elec. Energy</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>3,659,596
+Cr. 365.96</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>1,219,865
+Cr. 121.99</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>1,210,396
+Cr. 121.04</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>3,878,724
+Cr. 387.87</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>1,292,908
+Cr. 129.29</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>1,415,222
+Cr. 141.52</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>122,314
+Cr. 12.23</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>204,826
+Cr. 20.48</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>PU - 31 - OF</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>154,625
+Cr. 15.46</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>51,542
+Cr. 5.15</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>25,217
+Cr. 2.52</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>95,273
+Cr. 9.53</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>31,758
+Cr. 3.18</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>65,408
+Cr. 6.54</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>33,650
+Cr. 3.37</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>40,191
+Cr. 4.02</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>PU - 32 - CP</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>3,775,796
+Cr. 377.58</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>1,258,599
+Cr. 125.86</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>1,584,718
+Cr. 158.47</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>3,254,310
+Cr. 325.43</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>1,084,770
+Cr. 108.48</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1,686,251
+Cr. 168.63</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>601,481
+Cr. 60.15</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>101,533
+Cr. 10.15</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>PU - 33 - TRDC</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>3,391,480
+Cr. 339.15</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>1,130,493
+Cr. 113.05</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>980,440
+Cr. 98.04</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2,625,440
+Cr. 262.54</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>875,147
+Cr. 87.51</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>692,234
+Cr. 69.22</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>-182,913
+Cr. -18.29</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>-288,206
+Cr. -28.82</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>PU - 36 - Excise Duty</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>203,822
+Cr. 20.38</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>67,941
+Cr. 6.79</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>51,519
+Cr. 5.15</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>155,548
+Cr. 15.55</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>51,849
+Cr. 5.18</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>17,415
+Cr. 1.74</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>-34,434
+Cr. -3.44</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>-34,104
+Cr. -3.41</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>PU - 38 - Sales Tax</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>161,025
+Cr. 16.10</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>53,675
+Cr. 5.37</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>38,116
+Cr. 3.81</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>95,829
+Cr. 9.58</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>31,943
+Cr. 3.19</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>44,460
+Cr. 4.45</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>12,517
+Cr. 1.25</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>6,344
+Cr. 0.63</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>PU - 39 - ATD</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>80
+Cr. 0.01</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>27
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>16
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>5
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>2
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>23
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>21
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>7
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>PU - 42 - ARR SALARY</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>12,543
+Cr. 1.25</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>4,181
+Cr. 0.42</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>7,971
 Cr. 0.80</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>5,667
-Cr. 0.57</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>PU - 08 - NPS</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>1,100,183
-Cr. 110.02</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>366,728
-Cr. 36.67</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>399,406
-Cr. 39.94</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>1,285,187
-Cr. 128.52</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>428,396
-Cr. 42.84</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>425,235
-Cr. 42.52</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>-3,161
-Cr. -0.32</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>25,829
-Cr. 2.58</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>PU - 10 - KMA</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>765,522
-Cr. 76.55</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>255,174
-Cr. 25.52</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>261,222
-Cr. 26.12</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>680,197
-Cr. 68.02</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>226,732
-Cr. 22.67</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>290,482
-Cr. 29.05</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>63,750
-Cr. 6.37</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>29,260
-Cr. 2.93</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>PU - 11 - OT</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>96,309
-Cr. 9.63</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>32,103
-Cr. 3.21</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>62,375
-Cr. 6.24</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>77,300
-Cr. 7.73</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>25,767
-Cr. 2.58</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>54,545
-Cr. 5.45</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>28,778
-Cr. 2.88</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>-7,830
-Cr. -0.78</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>PU - 12 - NDA</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>280,806
-Cr. 28.08</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>93,602
-Cr. 9.36</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>93,733
-Cr. 9.37</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>209,913
-Cr. 20.99</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>69,971
-Cr. 7.00</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>98,022
-Cr. 9.80</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>28,051
-Cr. 2.81</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>4,289
-Cr. 0.43</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>PU - 13 - OA</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>551,574
-Cr. 55.16</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>183,858
-Cr. 18.39</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>253,677
-Cr. 25.37</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>527,832
-Cr. 52.78</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>175,944
-Cr. 17.59</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>250,792
-Cr. 25.08</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>74,848
-Cr. 7.48</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>-2,885
-Cr. -0.29</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>PU - 14 - FEES &amp; HON.</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>4,686
-Cr. 0.47</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>1,562
-Cr. 0.16</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>322
-Cr. 0.03</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>3,566
-Cr. 0.36</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>1,189
-Cr. 0.12</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>380
-Cr. 0.04</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>-809
-Cr. -0.08</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>58
-Cr. 0.01</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>PU - 15 - TA</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>19,866
-Cr. 1.99</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>6,622
-Cr. 0.66</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>10,277
-Cr. 1.03</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>16,048
-Cr. 1.60</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>5,349
-Cr. 0.53</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>9,177
-Cr. 0.92</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>3,828
-Cr. 0.38</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>-1,100
-Cr. -0.11</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>PU - 16 - TE</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>523,466
-Cr. 52.35</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>174,489
-Cr. 17.45</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>165,458
-Cr. 16.55</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>308,081
-Cr. 30.81</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>102,694
-Cr. 10.27</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>176,121
-Cr. 17.61</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>73,427
-Cr. 7.34</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>10,663
-Cr. 1.07</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>PU - 17 - ATPP</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2,260
-Cr. 0.23</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>753
-Cr. 0.08</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>2,110
-Cr. 0.21</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>703
-Cr. 0.07</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>-703
-Cr. -0.07</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>PU - 18 - OE</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>8,037
-Cr. 0.80</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2,679
-Cr. 0.27</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>8,252
-Cr. 0.83</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>2,751
-Cr. 0.28</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>-2,751
-Cr. -0.28</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>PU - 19 - Phone</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>606
-Cr. 0.06</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>202
-Cr. 0.02</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>655
-Cr. 0.07</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>218
-Cr. 0.02</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>-218
-Cr. -0.02</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>PU - 20 - Leave Salary</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>14,388
-Cr. 1.44</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>4,796
-Cr. 0.48</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>5,170
-Cr. 0.52</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>18,623
-Cr. 1.86</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>6,208
-Cr. 0.62</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>10,194
-Cr. 1.02</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>3,986
-Cr. 0.40</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>5,024
-Cr. 0.50</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>PU - 21 - Adv Expenses</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2,848
-Cr. 0.28</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>949
-Cr. 0.09</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>3,300
-Cr. 0.33</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>1,100
-Cr. 0.11</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>521
-Cr. 0.05</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>-579
-Cr. -0.06</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>521
-Cr. 0.05</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>PU - 22 - Util(excl. elec.)</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>PU - 23 - Rental Office Equip</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>40
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>13
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>42
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>14
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>-14
-Cr. -0.00</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>PU - 24 - Printing and Stnry</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>12
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>4
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>215
-Cr. 0.02</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>72
-Cr. 0.01</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>-72
-Cr. -0.01</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>PU - 25 - Children Edu. Allow</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>364,718
-Cr. 36.47</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>121,573
-Cr. 12.16</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>354,718
-Cr. 35.47</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>379,418
-Cr. 37.94</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>126,473
-Cr. 12.65</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>358,456
-Cr. 35.85</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>231,983
-Cr. 23.20</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>3,738
-Cr. 0.37</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>PU - 26 - Medical Expenses</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>321,438
-Cr. 32.14</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>107,146
-Cr. 10.71</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>142,245
-Cr. 14.22</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>384,392
-Cr. 38.44</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>128,131
-Cr. 12.81</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>124,789
-Cr. 12.48</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>-3,342
-Cr. -0.33</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>-17,456
-Cr. -1.75</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>PU - 27 - Materials from stock</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>1,445,603
-Cr. 144.56</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>481,868
-Cr. 48.19</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>376,832
-Cr. 37.68</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>1,068,752
-Cr. 106.88</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>356,251
-Cr. 35.63</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>588,317
-Cr. 58.83</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>232,066
-Cr. 23.21</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>211,485
-Cr. 21.15</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>PU - 28 - Materials-Dir. purchase</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>223,635
-Cr. 22.36</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>74,545
-Cr. 7.45</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>66,042
-Cr. 6.60</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>149,947
-Cr. 14.99</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>49,982
-Cr. 5.00</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>63,019
-Cr. 6.30</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>13,037
-Cr. 1.30</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>-3,023
-Cr. -0.30</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>PU - 29 - Remu. Re-engaged Staff</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>4
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>0
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>321
-Cr. 0.03</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>321
-Cr. 0.03</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>317
-Cr. 0.03</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>PU - 30 - Cost Of Elec. Energy</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>3,659,596
-Cr. 365.96</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>1,219,865
-Cr. 121.99</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>1,210,396
-Cr. 121.04</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>3,878,724
-Cr. 387.87</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>1,292,908
-Cr. 129.29</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>1,100,221
-Cr. 110.02</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>-192,687
-Cr. -19.27</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>-110,175
-Cr. -11.02</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>PU - 31 - OF</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>154,625
-Cr. 15.46</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>51,542
-Cr. 5.15</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>25,217
-Cr. 2.52</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>95,273
-Cr. 9.53</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>31,758
-Cr. 3.18</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>23,900
-Cr. 2.39</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>-7,858
-Cr. -0.79</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>-1,317
-Cr. -0.13</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>PU - 32 - CP</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>3,775,796
-Cr. 377.58</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>1,258,599
-Cr. 125.86</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>1,584,718
-Cr. 158.47</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>3,254,310
-Cr. 325.43</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>1,084,770
-Cr. 108.48</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1,658,468
-Cr. 165.85</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>573,698
-Cr. 57.37</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>73,750
-Cr. 7.38</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>PU - 33 - TRDC</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>3,391,480
-Cr. 339.15</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>1,130,493
-Cr. 113.05</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>980,440
-Cr. 98.04</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>2,625,440
-Cr. 262.54</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>875,147
-Cr. 87.51</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>534,260
-Cr. 53.43</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>-340,887
-Cr. -34.09</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>-446,180
-Cr. -44.62</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>PU - 36 - Excise Duty</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>203,822
-Cr. 20.38</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>67,941
-Cr. 6.79</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>51,519
-Cr. 5.15</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>155,548
-Cr. 15.55</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>51,849
-Cr. 5.18</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>11,736
-Cr. 1.17</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>-40,113
-Cr. -4.01</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>-39,783
-Cr. -3.98</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>PU - 38 - Sales Tax</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>161,025
-Cr. 16.10</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>53,675
-Cr. 5.37</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>38,116
-Cr. 3.81</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>95,829
-Cr. 9.58</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>31,943
-Cr. 3.19</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>30,820
-Cr. 3.08</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>-1,123
-Cr. -0.11</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>-7,296
-Cr. -0.73</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>PU - 39 - ATD</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>80
-Cr. 0.01</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>27
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>16
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>5
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>2
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>23
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>21
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>7
-Cr. 0.00</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>PU - 42 - ARR SALARY</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>12,543
-Cr. 1.25</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>4,181
-Cr. 0.42</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>7,971
-Cr. 0.80</t>
-        </is>
-      </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>25,882
@@ -6485,30 +6485,30 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>1,807,074
-Cr. 180.71</t>
+          <t>2,303,206
+Cr. 230.32</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>239,289
-Cr. 23.93</t>
+          <t>735,421
+Cr. 73.54</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>13,639
-Cr. 1.36</t>
+          <t>509,771
+Cr. 50.98</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -6550,30 +6550,30 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>32,192
-Cr. 3.22</t>
+          <t>32,998
+Cr. 3.30</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>21,416
-Cr. 2.14</t>
+          <t>22,222
+Cr. 2.22</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>28,447
-Cr. 2.84</t>
+          <t>29,253
+Cr. 2.93</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -6615,30 +6615,30 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>32,192
-Cr. 3.22</t>
+          <t>32,998
+Cr. 3.30</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>21,548
-Cr. 2.15</t>
+          <t>22,354
+Cr. 2.24</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>28,448
-Cr. 2.84</t>
+          <t>29,254
+Cr. 2.93</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -6745,24 +6745,24 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>36,811
+          <t>36,849
 Cr. 3.68</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>28,112
+          <t>28,150
 Cr. 2.81</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>30,466
+          <t>30,504
 Cr. 3.05</t>
         </is>
       </c>
@@ -6810,30 +6810,30 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-466,260
-Cr. -46.63</t>
+          <t>-481,299
+Cr. -48.13</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>84,680
-Cr. 8.47</t>
+          <t>69,641
+Cr. 6.96</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-19,830
-Cr. -1.98</t>
+          <t>-34,869
+Cr. -3.49</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -6875,30 +6875,30 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>2,079,500
-Cr. 207.95</t>
+          <t>2,101,259
+Cr. 210.13</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>1,480,307
-Cr. 148.03</t>
+          <t>1,502,066
+Cr. 150.21</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>-49,035
-Cr. -4.90</t>
+          <t>-27,276
+Cr. -2.73</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -6940,30 +6940,30 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>14,048,967
-Cr. 1404.90</t>
+          <t>15,263,467
+Cr. 1526.35</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>3,188,024
-Cr. 318.80</t>
+          <t>4,402,524
+Cr. 440.25</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>141</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>162,099
-Cr. 16.21</t>
+          <t>1,376,599
+Cr. 137.66</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -6992,14 +6992,14 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - JUL 2026 | uploaded 2026-08-25T15:43:05+05:30</t>
+          <t>Demand Previous Year Comparison - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -7171,30 +7171,30 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>232,594
-Cr. 23.26</t>
+          <t>236,563
+Cr. 23.66</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>18,753
-Cr. 1.88</t>
+          <t>22,722
+Cr. 2.27</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>17,046
-Cr. 1.70</t>
+          <t>21,015
+Cr. 2.10</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -7241,25 +7241,25 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1,467,818
-Cr. 146.78</t>
+          <t>1,473,830
+Cr. 147.38</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>264,851
-Cr. 26.49</t>
+          <t>270,863
+Cr. 27.09</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>154,024
-Cr. 15.40</t>
+          <t>160,036
+Cr. 16.00</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -7381,30 +7381,30 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>722,606
-Cr. 72.26</t>
+          <t>765,060
+Cr. 76.51</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>271,412
-Cr. 27.14</t>
+          <t>313,866
+Cr. 31.39</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>170</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>212,251
-Cr. 21.23</t>
+          <t>254,705
+Cr. 25.47</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -7451,30 +7451,30 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>800,112
-Cr. 80.01</t>
+          <t>838,163
+Cr. 83.82</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>113,462
-Cr. 11.35</t>
+          <t>151,513
+Cr. 15.15</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>119,850
-Cr. 11.98</t>
+          <t>157,901
+Cr. 15.79</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -7521,30 +7521,30 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,562,964
-Cr. 156.30</t>
+          <t>1,617,389
+Cr. 161.74</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>445,442
-Cr. 44.54</t>
+          <t>499,867
+Cr. 49.99</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>145</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>309,984
-Cr. 31.00</t>
+          <t>364,409
+Cr. 36.44</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -7591,25 +7591,25 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1,777,301
-Cr. 177.73</t>
+          <t>1,782,151
+Cr. 178.22</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>301,046
-Cr. 30.10</t>
+          <t>305,896
+Cr. 30.59</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>140,141
-Cr. 14.01</t>
+          <t>144,991
+Cr. 14.50</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -7661,30 +7661,30 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>3,545,213
-Cr. 354.52</t>
+          <t>4,605,644
+Cr. 460.56</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>-323,856
-Cr. -32.39</t>
+          <t>736,575
+Cr. 73.66</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>119</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>-634,533
-Cr. -63.45</t>
+          <t>425,898
+Cr. 42.59</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -7731,25 +7731,25 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>807,750
-Cr. 80.78</t>
+          <t>810,746
+Cr. 81.07</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>343,473
-Cr. 34.35</t>
+          <t>346,469
+Cr. 34.65</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>175</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>63,439
-Cr. 6.34</t>
+          <t>66,435
+Cr. 6.64</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -7801,25 +7801,25 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>355,867
-Cr. 35.59</t>
+          <t>356,769
+Cr. 35.68</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>24,321
-Cr. 2.43</t>
+          <t>25,223
+Cr. 2.52</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>31,655
-Cr. 3.17</t>
+          <t>32,557
+Cr. 3.26</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -7937,30 +7937,30 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>12,479,934
-Cr. 1247.99</t>
+          <t>13,694,024
+Cr. 1369.40</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>1,614,643
-Cr. 161.46</t>
+          <t>2,828,733
+Cr. 282.87</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>229,047
-Cr. 22.90</t>
+          <t>1,443,137
+Cr. 144.31</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -8007,30 +8007,30 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>1,569,032
-Cr. 156.90</t>
+          <t>1,569,443
+Cr. 156.94</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>1,573,380
-Cr. 157.34</t>
+          <t>1,573,791
+Cr. 157.38</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-36084</t>
+          <t>-36093</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>-66,951
-Cr. -6.70</t>
+          <t>-66,540
+Cr. -6.65</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>-12028</t>
+          <t>-12031</t>
         </is>
       </c>
     </row>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - JUL 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Staff Current Year - JUL 202" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Non Staff Current Year - JUL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Previous Year Comparison - J" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand SMH Wise - AUG 2026 | up" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Staff Current Year - AUG 202" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Non Staff Current Year - AUG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PU Previous Year Comparison - A" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand Previous Year Comparison" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -555,14 +555,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUL 2026</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUL 2026</t>
+Actuals up to AUG 2026</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -613,36 +613,36 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>240,031
-Cr. 24.00</t>
+          <t>267,301
+Cr. 26.73</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>236,563
-Cr. 23.66</t>
+          <t>294,025
+Cr. 29.40</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>-3,468
-Cr. -0.35</t>
+          <t>26,724
+Cr. 2.67</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>404,959
-Cr. 40.50</t>
+          <t>347,497
+Cr. 34.75</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -665,36 +665,36 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,177,984
-Cr. 117.80</t>
+          <t>1,503,709
+Cr. 150.37</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,473,830
-Cr. 147.38</t>
+          <t>1,779,391
+Cr. 177.94</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>295,846
-Cr. 29.58</t>
+          <t>275,682
+Cr. 27.57</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>2,135,072
-Cr. 213.51</t>
+          <t>1,829,511
+Cr. 182.95</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -717,8 +717,8 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>923,741
-Cr. 92.37</t>
+          <t>777,018
+Cr. 77.70</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -729,13 +729,13 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>-141,709
-Cr. -14.17</t>
+          <t>5,014
+Cr. 0.50</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -769,36 +769,36 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>413,960
-Cr. 41.40</t>
+          <t>563,992
+Cr. 56.40</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>765,059
-Cr. 76.51</t>
+          <t>882,060
+Cr. 88.21</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>351,099
-Cr. 35.11</t>
+          <t>318,068
+Cr. 31.81</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>588,522
-Cr. 58.85</t>
+          <t>471,521
+Cr. 47.15</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -821,36 +821,36 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>694,140
-Cr. 69.41</t>
+          <t>858,312
+Cr. 85.83</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>838,163
-Cr. 83.82</t>
+          <t>987,240
+Cr. 98.72</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>144,023
-Cr. 14.40</t>
+          <t>128,928
+Cr. 12.89</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,221,787
-Cr. 122.18</t>
+          <t>1,072,710
+Cr. 107.27</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -873,36 +873,36 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1,217,272
-Cr. 121.73</t>
+          <t>1,396,902
+Cr. 139.69</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,617,389
-Cr. 161.74</t>
+          <t>1,953,133
+Cr. 195.31</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>400,117
-Cr. 40.01</t>
+          <t>556,231
+Cr. 55.62</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,735,177
-Cr. 173.52</t>
+          <t>1,399,433
+Cr. 139.94</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -925,36 +925,36 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1,511,191
-Cr. 151.12</t>
+          <t>1,845,319
+Cr. 184.53</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1,782,151
-Cr. 178.22</t>
+          <t>2,193,589
+Cr. 219.36</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>270,960
-Cr. 27.10</t>
+          <t>348,270
+Cr. 34.83</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,646,615
-Cr. 264.66</t>
+          <t>2,235,177
+Cr. 223.52</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -977,31 +977,31 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>3,862,305
-Cr. 386.23</t>
+          <t>4,836,336
+Cr. 483.63</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4,605,644
-Cr. 460.56</t>
+          <t>4,657,805
+Cr. 465.78</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>743,339
-Cr. 74.33</t>
+          <t>-178,531
+Cr. -17.85</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>7,001,562
-Cr. 700.16</t>
+          <t>6,949,401
+Cr. 694.94</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1029,36 +1029,36 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>598,674
-Cr. 59.87</t>
+          <t>580,347
+Cr. 58.03</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>810,746
-Cr. 81.07</t>
+          <t>915,762
+Cr. 91.58</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>212,072
-Cr. 21.21</t>
+          <t>335,415
+Cr. 33.54</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>582,086
-Cr. 58.21</t>
+          <t>477,070
+Cr. 47.71</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -1081,36 +1081,36 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>325,688
-Cr. 32.57</t>
+          <t>414,432
+Cr. 41.44</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>356,768
-Cr. 35.68</t>
+          <t>439,544
+Cr. 43.95</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>31,080
-Cr. 3.11</t>
+          <t>25,112
+Cr. 2.51</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>637,870
-Cr. 63.79</t>
+          <t>555,094
+Cr. 55.51</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -1133,36 +1133,36 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>388,570
-Cr. 38.86</t>
+          <t>537,945
+Cr. 53.79</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>425,678
-Cr. 42.57</t>
+          <t>532,662
+Cr. 53.27</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>37,108
-Cr. 3.71</t>
+          <t>-5,283
+Cr. -0.53</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>865,389
-Cr. 86.54</t>
+          <t>758,405
+Cr. 75.84</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1181,36 +1181,36 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>11,353,556
-Cr. 1135.36</t>
+          <t>13,581,613
+Cr. 1358.16</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>13,694,023
-Cr. 1369.40</t>
+          <t>15,417,243
+Cr. 1541.72</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2,340,467
-Cr. 234.05</t>
+          <t>1,835,630
+Cr. 183.56</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>18,901,850
-Cr. 1890.18</t>
+          <t>17,178,630
+Cr. 1717.86</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -1233,36 +1233,36 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1,362,799
-Cr. 136.28</t>
+          <t>-5,435
+Cr. -0.54</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,569,443
-Cr. 156.94</t>
+          <t>1,578,852
+Cr. 157.89</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>206,644
-Cr. 20.66</t>
+          <t>1,584,287
+Cr. 158.43</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>-29050</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,582,488
-Cr. -158.25</t>
+          <t>-1,591,897
+Cr. -159.19</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12031</t>
+          <t>-12103</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -1294,7 +1294,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1346,14 +1346,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUL 2026</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUL 2026</t>
+Actuals up to AUG 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1399,36 +1399,36 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2,249,064
-Cr. 224.91</t>
+          <t>2,794,337
+Cr. 279.43</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2,453,873
-Cr. 245.39</t>
+          <t>3,073,272
+Cr. 307.33</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>204,809
-Cr. 20.48</t>
+          <t>278,935
+Cr. 27.89</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>4,252,536
-Cr. 425.25</t>
+          <t>3,633,137
+Cr. 363.31</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -1446,36 +1446,36 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1,359,404
-Cr. 135.94</t>
+          <t>1,708,522
+Cr. 170.85</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,579,536
-Cr. 157.95</t>
+          <t>1,968,578
+Cr. 196.86</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>220,132
-Cr. 22.01</t>
+          <t>260,056
+Cr. 26.01</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,520,917
-Cr. 252.09</t>
+          <t>2,131,875
+Cr. 213.19</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -1493,8 +1493,8 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>118,787
+Cr. 11.88</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1505,8 +1505,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>81
-Cr. 0.01</t>
+          <t>-118,706
+Cr. -11.87</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1540,36 +1540,36 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>268,852
-Cr. 26.89</t>
+          <t>323,416
+Cr. 32.34</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>269,887
-Cr. 26.99</t>
+          <t>337,922
+Cr. 33.79</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1,035
-Cr. 0.10</t>
+          <t>14,506
+Cr. 1.45</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>506,311
-Cr. 50.63</t>
+          <t>438,276
+Cr. 43.83</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -1587,36 +1587,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>167,312
-Cr. 16.73</t>
+          <t>206,920
+Cr. 20.69</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>173,467
-Cr. 17.35</t>
+          <t>216,618
+Cr. 21.66</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>6,155
-Cr. 0.62</t>
+          <t>9,698
+Cr. 0.97</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>323,142
-Cr. 32.31</t>
+          <t>279,991
+Cr. 28.00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -1634,36 +1634,36 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>386,836
-Cr. 38.68</t>
+          <t>535,495
+Cr. 53.55</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>425,236
-Cr. 42.52</t>
+          <t>532,040
+Cr. 53.20</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>38,400
-Cr. 3.84</t>
+          <t>-3,455
+Cr. -0.35</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>859,951
-Cr. 86.00</t>
+          <t>753,147
+Cr. 75.31</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1681,36 +1681,36 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>255,207
-Cr. 25.52</t>
+          <t>283,415
+Cr. 28.34</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>290,482
-Cr. 29.05</t>
+          <t>364,653
+Cr. 36.47</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>35,275
-Cr. 3.53</t>
+          <t>81,238
+Cr. 8.12</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>389,715
-Cr. 38.97</t>
+          <t>315,544
+Cr. 31.55</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -1728,36 +1728,36 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>26,924
-Cr. 2.69</t>
+          <t>32,208
+Cr. 3.22</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>54,782
-Cr. 5.48</t>
+          <t>59,582
+Cr. 5.96</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>27,858
-Cr. 2.79</t>
+          <t>27,374
+Cr. 2.74</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>22,518
-Cr. 2.25</t>
+          <t>17,718
+Cr. 1.77</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -1775,36 +1775,36 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>69,543
-Cr. 6.95</t>
+          <t>87,464
+Cr. 8.75</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>98,022
-Cr. 9.80</t>
+          <t>122,506
+Cr. 12.25</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>28,479
-Cr. 2.85</t>
+          <t>35,042
+Cr. 3.50</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>111,891
-Cr. 11.19</t>
+          <t>87,407
+Cr. 8.74</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -1822,36 +1822,36 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>273,477
-Cr. 27.35</t>
+          <t>219,930
+Cr. 21.99</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>250,736
-Cr. 25.07</t>
+          <t>279,175
+Cr. 27.92</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>-22,741
-Cr. -2.27</t>
+          <t>59,245
+Cr. 5.92</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>277,096
-Cr. 27.71</t>
+          <t>248,657
+Cr. 24.87</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -1869,36 +1869,36 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>1,257
-Cr. 0.13</t>
+          <t>1,486
+Cr. 0.15</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>381
+          <t>427
 Cr. 0.04</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-876
-Cr. -0.09</t>
+          <t>-1,059
+Cr. -0.11</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>3,185
-Cr. 0.32</t>
+          <t>3,139
+Cr. 0.31</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1916,36 +1916,36 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>5,665
-Cr. 0.57</t>
+          <t>6,687
+Cr. 0.67</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>9,177
-Cr. 0.92</t>
+          <t>11,132
+Cr. 1.11</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3,512
-Cr. 0.35</t>
+          <t>4,445
+Cr. 0.44</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>6,871
-Cr. 0.69</t>
+          <t>4,916
+Cr. 0.49</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -1963,36 +1963,36 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>100,083
-Cr. 10.01</t>
+          <t>128,367
+Cr. 12.84</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>176,120
-Cr. 17.61</t>
+          <t>217,182
+Cr. 21.72</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>76,037
-Cr. 7.60</t>
+          <t>88,815
+Cr. 8.88</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>169</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>131,961
-Cr. 13.20</t>
+          <t>90,899
+Cr. 9.09</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -2010,8 +2010,8 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>704
-Cr. 0.07</t>
+          <t>879
+Cr. 0.09</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2022,8 +2022,8 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>-704
-Cr. -0.07</t>
+          <t>-879
+Cr. -0.09</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2057,36 +2057,36 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>5,393
-Cr. 0.54</t>
+          <t>7,760
+Cr. 0.78</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>10,103
-Cr. 1.01</t>
+          <t>12,682
+Cr. 1.27</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>4,710
-Cr. 0.47</t>
+          <t>4,922
+Cr. 0.49</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>163</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>8,520
-Cr. 0.85</t>
+          <t>5,941
+Cr. 0.59</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -2104,36 +2104,36 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>320,448
-Cr. 32.04</t>
+          <t>158,091
+Cr. 15.81</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>358,455
-Cr. 35.85</t>
+          <t>374,892
+Cr. 37.49</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>38,007
-Cr. 3.80</t>
+          <t>216,801
+Cr. 21.68</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>20,963
-Cr. 2.10</t>
+          <t>4,526
+Cr. 0.45</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -2151,36 +2151,36 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>125,215
-Cr. 12.52</t>
+          <t>160,163
+Cr. 16.02</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>125,964
-Cr. 12.60</t>
+          <t>152,898
+Cr. 15.29</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>749
-Cr. 0.07</t>
+          <t>-7,265
+Cr. -0.73</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>95</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>258,428
-Cr. 25.84</t>
+          <t>231,494
+Cr. 23.15</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -2204,14 +2204,14 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>321
-Cr. 0.03</t>
+          <t>476
+Cr. 0.05</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>321
-Cr. 0.03</t>
+          <t>476
+Cr. 0.05</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2221,8 +2221,8 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>-321
-Cr. -0.03</t>
+          <t>-476
+Cr. -0.05</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>20
+          <t>2
 Cr. 0.00</t>
         </is>
       </c>
@@ -2257,13 +2257,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>3
+          <t>21
 Cr. 0.00</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2292,36 +2292,36 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>6,096
-Cr. 0.61</t>
+          <t>10,784
+Cr. 1.08</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>4,775
-Cr. 0.48</t>
+          <t>5,329
+Cr. 0.53</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>-1,321
-Cr. -0.13</t>
+          <t>-5,455
+Cr. -0.55</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>21,107
-Cr. 2.11</t>
+          <t>20,553
+Cr. 2.06</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -2339,36 +2339,36 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2,748
-Cr. 0.27</t>
+          <t>5,002
+Cr. 0.50</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2,298
-Cr. 0.23</t>
+          <t>2,572
+Cr. 0.26</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>-450
-Cr. -0.04</t>
+          <t>-2,430
+Cr. -0.24</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>9,707
-Cr. 0.97</t>
+          <t>9,433
+Cr. 0.94</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -2386,8 +2386,8 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>3,448
-Cr. 0.34</t>
+          <t>4,829
+Cr. 0.48</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2398,13 +2398,13 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>221,300
-Cr. 22.13</t>
+          <t>219,919
+Cr. 21.99</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2433,36 +2433,36 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>52
-Cr. 0.01</t>
+          <t>256
+Cr. 0.03</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>1,141
-Cr. 0.11</t>
+          <t>1,705
+Cr. 0.17</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>1,089
-Cr. 0.11</t>
+          <t>1,449
+Cr. 0.14</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>666</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-527
-Cr. -0.05</t>
+          <t>-1,091
+Cr. -0.11</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>278</t>
         </is>
       </c>
     </row>
@@ -2480,36 +2480,36 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>5,627,748
-Cr. 562.77</t>
+          <t>6,794,800
+Cr. 679.48</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>6,509,608
-Cr. 650.96</t>
+          <t>7,958,493
+Cr. 795.85</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>881,860
-Cr. 88.19</t>
+          <t>1,163,693
+Cr. 116.37</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>9,797,912
-Cr. 979.79</t>
+          <t>8,349,027
+Cr. 834.90</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2593,14 +2593,14 @@
         <is>
           <t>B
 BP
-BP UPTO JUL 2026</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 AE
-Actuals Upto JUL 2026</t>
+Actuals up to AUG 2026</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2646,8 +2646,8 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2,767
-Cr. 0.28</t>
+          <t>3,438
+Cr. 0.34</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2658,8 +2658,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>-2,767
-Cr. -0.28</t>
+          <t>-3,438
+Cr. -0.34</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2693,8 +2693,8 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>201
-Cr. 0.02</t>
+          <t>273
+Cr. 0.03</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2705,8 +2705,8 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>-201
-Cr. -0.02</t>
+          <t>-273
+Cr. -0.03</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2740,8 +2740,8 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>992
-Cr. 0.10</t>
+          <t>1,375
+Cr. 0.14</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -2752,8 +2752,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-992
-Cr. -0.10</t>
+          <t>-1,375
+Cr. -0.14</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>13
+          <t>18
 Cr. 0.00</t>
         </is>
       </c>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-13
+          <t>-18
 Cr. -0.00</t>
         </is>
       </c>
@@ -2881,8 +2881,8 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>4
-Cr. 0.00</t>
+          <t>90
+Cr. 0.01</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2893,8 +2893,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>-4
-Cr. -0.00</t>
+          <t>-90
+Cr. -0.01</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2928,36 +2928,36 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>350,722
-Cr. 35.07</t>
+          <t>445,313
+Cr. 44.53</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>737,391
-Cr. 73.74</t>
+          <t>746,612
+Cr. 74.66</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>386,669
-Cr. 38.67</t>
+          <t>301,299
+Cr. 30.13</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>331,361
-Cr. 33.14</t>
+          <t>322,140
+Cr. 32.21</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -2975,36 +2975,36 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>52,719
-Cr. 5.27</t>
+          <t>62,478
+Cr. 6.25</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>63,087
-Cr. 6.31</t>
+          <t>70,596
+Cr. 7.06</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>10,368
-Cr. 1.04</t>
+          <t>8,118
+Cr. 0.81</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>86,860
-Cr. 8.69</t>
+          <t>79,351
+Cr. 7.94</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -3022,36 +3022,36 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1,330,274
-Cr. 133.03</t>
+          <t>1,616,135
+Cr. 161.61</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1,415,221
-Cr. 141.52</t>
+          <t>1,504,722
+Cr. 150.47</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>84,947
-Cr. 8.49</t>
+          <t>-111,413
+Cr. -11.14</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2,463,503
-Cr. 246.35</t>
+          <t>2,374,002
+Cr. 237.40</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -3069,36 +3069,36 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>31,159
-Cr. 3.12</t>
+          <t>39,697
+Cr. 3.97</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>65,407
-Cr. 6.54</t>
+          <t>66,725
+Cr. 6.67</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>34,248
-Cr. 3.42</t>
+          <t>27,028
+Cr. 2.70</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>29,866
-Cr. 2.99</t>
+          <t>28,548
+Cr. 2.85</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -3116,36 +3116,36 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>1,396,328
-Cr. 139.63</t>
+          <t>1,355,962
+Cr. 135.60</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1,686,250
-Cr. 168.62</t>
+          <t>1,822,493
+Cr. 182.25</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>289,922
-Cr. 28.99</t>
+          <t>466,531
+Cr. 46.65</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>134</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1,568,060
-Cr. 156.81</t>
+          <t>1,431,817
+Cr. 143.18</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -3163,8 +3163,8 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>877,350
-Cr. 87.73</t>
+          <t>1,093,933
+Cr. 109.39</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -3175,13 +3175,13 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-185,115
-Cr. -18.51</t>
+          <t>-401,698
+Cr. -40.17</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3210,8 +3210,8 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>49,308
-Cr. 4.93</t>
+          <t>64,812
+Cr. 6.48</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -3222,13 +3222,13 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-31,894
-Cr. -3.19</t>
+          <t>-47,398
+Cr. -4.74</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3257,8 +3257,8 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>31,700
-Cr. 3.17</t>
+          <t>39,929
+Cr. 3.99</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -3269,13 +3269,13 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>12,760
-Cr. 1.28</t>
+          <t>4,531
+Cr. 0.45</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -3304,8 +3304,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>288
-Cr. 0.03</t>
+          <t>227
+Cr. 0.02</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3316,13 +3316,13 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>6,094
-Cr. 0.61</t>
+          <t>6,155
+Cr. 0.62</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3398,8 +3398,8 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>1,538,432
-Cr. 153.84</t>
+          <t>1,959,732
+Cr. 195.97</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3410,13 +3410,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>764,774
-Cr. 76.48</t>
+          <t>343,474
+Cr. 34.35</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3445,36 +3445,36 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>6,855
-Cr. 0.69</t>
+          <t>13,470
+Cr. 1.35</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>32,998
-Cr. 3.30</t>
+          <t>37,201
+Cr. 3.72</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>26,143
-Cr. 2.61</t>
+          <t>23,731
+Cr. 2.37</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>-669
-Cr. -0.07</t>
+          <t>-4,872
+Cr. -0.49</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -3492,36 +3492,36 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>6,788
-Cr. 0.68</t>
+          <t>13,305
+Cr. 1.33</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>32,998
-Cr. 3.30</t>
+          <t>37,201
+Cr. 3.72</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>26,210
-Cr. 2.62</t>
+          <t>23,896
+Cr. 2.39</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>280</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-1,066
-Cr. -0.11</t>
+          <t>-5,269
+Cr. -0.53</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>4
+          <t>2
 Cr. 0.00</t>
         </is>
       </c>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>-4
+          <t>-2
 Cr. -0.00</t>
         </is>
       </c>
@@ -3586,36 +3586,36 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4,748
-Cr. 0.47</t>
+          <t>10,874
+Cr. 1.09</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>36,849
-Cr. 3.68</t>
+          <t>41,871
+Cr. 4.19</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>32,101
-Cr. 3.21</t>
+          <t>30,997
+Cr. 3.10</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>385</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-10,751
-Cr. -1.08</t>
+          <t>-15,773
+Cr. -1.58</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -3633,36 +3633,36 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>-27,982
-Cr. -2.80</t>
+          <t>-688,675
+Cr. -68.87</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>-481,300
-Cr. -48.13</t>
+          <t>-623,357
+Cr. -62.34</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>-453,318
-Cr. -45.33</t>
+          <t>65,318
+Cr. 6.53</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>-1,171,521
-Cr. -117.15</t>
+          <t>-1,029,464
+Cr. -102.95</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -3680,36 +3680,36 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>1,435,937
-Cr. 143.59</t>
+          <t>748,991
+Cr. 74.90</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2,101,259
-Cr. 210.13</t>
+          <t>2,269,838
+Cr. 226.98</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>665,322
-Cr. 66.53</t>
+          <t>1,520,847
+Cr. 152.08</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>303</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-303,680
-Cr. -30.37</t>
+          <t>-472,259
+Cr. -47.23</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -3727,36 +3727,36 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>7,088,607
-Cr. 708.86</t>
+          <t>6,781,379
+Cr. 678.14</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>8,753,857
-Cr. 875.39</t>
+          <t>9,037,599
+Cr. 903.76</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>1,665,250
-Cr. 166.53</t>
+          <t>2,256,220
+Cr. 225.62</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>7,521,451
-Cr. 752.15</t>
+          <t>7,237,709
+Cr. 723.77</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -3778,20 +3778,20 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3852,14 +3852,14 @@
         <is>
           <t>B
 Previous Budget Proportion
-A / 12 * 4</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>C
 Previous Actual Expenditure
-Upto JUL 2025</t>
+up to AUG 2025</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3873,14 +3873,14 @@
         <is>
           <t>E
 Current Budget Proportion
-D / 12 * 4</t>
+D / 12 * 5</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>F
 Current Actual Expenditure
-Upto JUL 2026</t>
+up to AUG 2026</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2,358,093
-Cr. 235.81</t>
+          <t>2,947,616
+Cr. 294.76</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2,424,646
-Cr. 242.46</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3944,20 +3944,20 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2,235,470
-Cr. 223.55</t>
+          <t>2,794,337
+Cr. 279.43</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2,453,873
-Cr. 245.39</t>
+          <t>3,073,271
+Cr. 307.33</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>218,403
-Cr. 21.84</t>
+          <t>278,934
+Cr. 27.89</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3967,13 +3967,13 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>29,227
-Cr. 2.92</t>
+          <t>3,073,271
+Cr. 307.33</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -3991,14 +3991,14 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1,473,411
-Cr. 147.34</t>
+          <t>1,841,764
+Cr. 184.18</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,435,879
-Cr. 143.59</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4009,36 +4009,36 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1,366,818
-Cr. 136.68</t>
+          <t>1,708,522
+Cr. 170.85</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1,579,536
-Cr. 157.95</t>
+          <t>1,968,578
+Cr. 196.86</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>212,718
-Cr. 21.27</t>
+          <t>260,056
+Cr. 26.01</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>143,657
-Cr. 14.37</t>
+          <t>1,968,578
+Cr. 196.86</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>96,610
-Cr. 9.66</t>
+          <t>120,763
+Cr. 12.08</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>218
-Cr. 0.02</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -4074,8 +4074,8 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>95,030
-Cr. 9.50</t>
+          <t>118,787
+Cr. 11.88</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -4086,8 +4086,8 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>-94,948
-Cr. -9.49</t>
+          <t>-118,705
+Cr. -11.87</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -4097,8 +4097,8 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>-136
-Cr. -0.01</t>
+          <t>82
+Cr. 0.01</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>274,971
-Cr. 27.50</t>
+          <t>343,713
+Cr. 34.37</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>264,372
-Cr. 26.44</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -4139,20 +4139,20 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>258,733
-Cr. 25.87</t>
+          <t>323,416
+Cr. 32.34</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>269,887
-Cr. 26.99</t>
+          <t>337,922
+Cr. 33.79</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>11,154
-Cr. 1.12</t>
+          <t>14,506
+Cr. 1.45</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -4162,13 +4162,13 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>5,515
-Cr. 0.55</t>
+          <t>337,922
+Cr. 33.79</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -4186,14 +4186,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>168,673
-Cr. 16.87</t>
+          <t>210,841
+Cr. 21.08</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>167,840
-Cr. 16.78</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4204,20 +4204,20 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>165,536
-Cr. 16.55</t>
+          <t>206,920
+Cr. 20.69</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>173,467
-Cr. 17.35</t>
+          <t>216,617
+Cr. 21.66</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>7,931
-Cr. 0.79</t>
+          <t>9,697
+Cr. 0.97</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -4227,13 +4227,13 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>5,627
-Cr. 0.56</t>
+          <t>216,617
+Cr. 21.66</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -4251,14 +4251,14 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>366,728
-Cr. 36.67</t>
+          <t>458,410
+Cr. 45.84</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>399,406
-Cr. 39.94</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -4269,20 +4269,20 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>428,396
-Cr. 42.84</t>
+          <t>535,495
+Cr. 53.55</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>425,235
-Cr. 42.52</t>
+          <t>532,039
+Cr. 53.20</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>-3,161
-Cr. -0.32</t>
+          <t>-3,456
+Cr. -0.35</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -4292,13 +4292,13 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>25,829
-Cr. 2.58</t>
+          <t>532,039
+Cr. 53.20</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -4316,14 +4316,14 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>255,174
-Cr. 25.52</t>
+          <t>318,968
+Cr. 31.90</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>261,222
-Cr. 26.12</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -4334,36 +4334,36 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>226,732
-Cr. 22.67</t>
+          <t>283,415
+Cr. 28.34</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>290,482
-Cr. 29.05</t>
+          <t>364,653
+Cr. 36.47</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>63,750
-Cr. 6.37</t>
+          <t>81,238
+Cr. 8.12</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>29,260
-Cr. 2.93</t>
+          <t>364,653
+Cr. 36.47</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -4381,14 +4381,14 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>32,103
-Cr. 3.21</t>
+          <t>40,129
+Cr. 4.01</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>62,375
-Cr. 6.24</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>25,767
-Cr. 2.58</t>
+          <t>32,208
+Cr. 3.22</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>54,782
-Cr. 5.48</t>
+          <t>59,582
+Cr. 5.96</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>29,015
-Cr. 2.90</t>
+          <t>27,374
+Cr. 2.74</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>185</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>-7,593
-Cr. -0.76</t>
+          <t>59,582
+Cr. 5.96</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -4446,14 +4446,14 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>93,602
-Cr. 9.36</t>
+          <t>117,002
+Cr. 11.70</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>93,733
-Cr. 9.37</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -4464,20 +4464,20 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>69,971
-Cr. 7.00</t>
+          <t>87,464
+Cr. 8.75</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>98,022
-Cr. 9.80</t>
+          <t>122,506
+Cr. 12.25</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>28,051
-Cr. 2.81</t>
+          <t>35,042
+Cr. 3.50</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -4487,13 +4487,13 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>4,289
-Cr. 0.43</t>
+          <t>122,506
+Cr. 12.25</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -4511,14 +4511,14 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>183,858
-Cr. 18.39</t>
+          <t>229,822
+Cr. 22.98</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>253,677
-Cr. 25.37</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -4529,36 +4529,36 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>175,944
-Cr. 17.59</t>
+          <t>219,930
+Cr. 21.99</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>250,736
-Cr. 25.07</t>
+          <t>279,175
+Cr. 27.92</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>74,792
-Cr. 7.48</t>
+          <t>59,245
+Cr. 5.92</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>127</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>-2,941
-Cr. -0.29</t>
+          <t>279,175
+Cr. 27.92</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -4576,14 +4576,14 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>1,562
-Cr. 0.16</t>
+          <t>1,952
+Cr. 0.20</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>322
-Cr. 0.03</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -4594,36 +4594,36 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>1,189
-Cr. 0.12</t>
+          <t>1,486
+Cr. 0.15</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>380
+          <t>426
 Cr. 0.04</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>-809
-Cr. -0.08</t>
+          <t>-1,060
+Cr. -0.11</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>58
-Cr. 0.01</t>
+          <t>426
+Cr. 0.04</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -4641,14 +4641,14 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>6,622
-Cr. 0.66</t>
+          <t>8,278
+Cr. 0.83</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>10,277
-Cr. 1.03</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -4659,36 +4659,36 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>5,349
-Cr. 0.53</t>
+          <t>6,687
+Cr. 0.67</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>9,177
-Cr. 0.92</t>
+          <t>11,132
+Cr. 1.11</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>3,828
-Cr. 0.38</t>
+          <t>4,445
+Cr. 0.44</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>166</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>-1,100
-Cr. -0.11</t>
+          <t>11,132
+Cr. 1.11</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -4706,14 +4706,14 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>174,489
-Cr. 17.45</t>
+          <t>218,111
+Cr. 21.81</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>165,458
-Cr. 16.55</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -4724,36 +4724,36 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>102,694
-Cr. 10.27</t>
+          <t>128,367
+Cr. 12.84</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>176,121
-Cr. 17.61</t>
+          <t>217,183
+Cr. 21.72</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>73,427
-Cr. 7.34</t>
+          <t>88,816
+Cr. 8.88</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>169</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>10,663
-Cr. 1.07</t>
+          <t>217,183
+Cr. 21.72</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -4771,8 +4771,8 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>753
-Cr. 0.08</t>
+          <t>942
+Cr. 0.09</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -4789,8 +4789,8 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>703
-Cr. 0.07</t>
+          <t>879
+Cr. 0.09</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -4801,8 +4801,8 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>-703
-Cr. -0.07</t>
+          <t>-879
+Cr. -0.09</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -4836,8 +4836,8 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2,679
-Cr. 0.27</t>
+          <t>3,349
+Cr. 0.33</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4854,8 +4854,8 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2,751
-Cr. 0.28</t>
+          <t>3,438
+Cr. 0.34</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -4866,8 +4866,8 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>-2,751
-Cr. -0.28</t>
+          <t>-3,438
+Cr. -0.34</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -4901,8 +4901,8 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>202
-Cr. 0.02</t>
+          <t>252
+Cr. 0.03</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -4919,8 +4919,8 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>218
-Cr. 0.02</t>
+          <t>273
+Cr. 0.03</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -4931,8 +4931,8 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>-218
-Cr. -0.02</t>
+          <t>-273
+Cr. -0.03</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -4966,14 +4966,14 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>4,796
-Cr. 0.48</t>
+          <t>5,995
+Cr. 0.60</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5,170
-Cr. 0.52</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -4984,20 +4984,20 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>6,208
-Cr. 0.62</t>
+          <t>7,760
+Cr. 0.78</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>10,103
-Cr. 1.01</t>
+          <t>12,682
+Cr. 1.27</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>3,895
-Cr. 0.39</t>
+          <t>4,922
+Cr. 0.49</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -5007,13 +5007,13 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>4,933
-Cr. 0.49</t>
+          <t>12,682
+Cr. 1.27</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -5031,8 +5031,8 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>949
-Cr. 0.09</t>
+          <t>1,187
+Cr. 0.12</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -5049,8 +5049,8 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>1,100
-Cr. 0.11</t>
+          <t>1,375
+Cr. 0.14</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -5061,8 +5061,8 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>-1,100
-Cr. -0.11</t>
+          <t>-1,375
+Cr. -0.14</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>13
+          <t>17
 Cr. 0.00</t>
         </is>
       </c>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>14
+          <t>18
 Cr. 0.00</t>
         </is>
       </c>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>-14
+          <t>-18
 Cr. -0.00</t>
         </is>
       </c>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4
+          <t>5
 Cr. 0.00</t>
         </is>
       </c>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>72
+          <t>90
 Cr. 0.01</t>
         </is>
       </c>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>-72
+          <t>-90
 Cr. -0.01</t>
         </is>
       </c>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>121,573
-Cr. 12.16</t>
+          <t>151,966
+Cr. 15.20</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>354,718
-Cr. 35.47</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -5309,36 +5309,36 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>126,473
-Cr. 12.65</t>
+          <t>158,091
+Cr. 15.81</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>358,456
-Cr. 35.85</t>
+          <t>374,893
+Cr. 37.49</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>231,983
-Cr. 23.20</t>
+          <t>216,802
+Cr. 21.68</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>3,738
-Cr. 0.37</t>
+          <t>374,893
+Cr. 37.49</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -5356,14 +5356,14 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>107,146
-Cr. 10.71</t>
+          <t>133,932
+Cr. 13.39</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>142,245
-Cr. 14.22</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -5374,36 +5374,36 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>128,131
-Cr. 12.81</t>
+          <t>160,163
+Cr. 16.02</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>125,963
-Cr. 12.60</t>
+          <t>152,897
+Cr. 15.29</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>-2,168
-Cr. -0.22</t>
+          <t>-7,266
+Cr. -0.73</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>-16,282
-Cr. -1.63</t>
+          <t>152,897
+Cr. 15.29</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -5421,14 +5421,14 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>481,868
-Cr. 48.19</t>
+          <t>602,335
+Cr. 60.23</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>376,832
-Cr. 37.68</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -5439,36 +5439,36 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>356,251
-Cr. 35.63</t>
+          <t>445,313
+Cr. 44.53</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>737,390
-Cr. 73.74</t>
+          <t>746,612
+Cr. 74.66</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>381,139
-Cr. 38.11</t>
+          <t>301,299
+Cr. 30.13</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>168</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>360,558
-Cr. 36.06</t>
+          <t>746,612
+Cr. 74.66</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -5486,14 +5486,14 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>74,545
-Cr. 7.45</t>
+          <t>93,181
+Cr. 9.32</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>66,042
-Cr. 6.60</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -5504,36 +5504,36 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>49,982
-Cr. 5.00</t>
+          <t>62,478
+Cr. 6.25</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>63,087
-Cr. 6.31</t>
+          <t>70,597
+Cr. 7.06</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>13,105
-Cr. 1.31</t>
+          <t>8,119
+Cr. 0.81</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>-2,955
-Cr. -0.30</t>
+          <t>70,597
+Cr. 7.06</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>4
+          <t>0
 Cr. 0.00</t>
         </is>
       </c>
@@ -5575,14 +5575,14 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>321
-Cr. 0.03</t>
+          <t>476
+Cr. 0.05</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>321
-Cr. 0.03</t>
+          <t>476
+Cr. 0.05</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -5592,8 +5592,8 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>317
-Cr. 0.03</t>
+          <t>476
+Cr. 0.05</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -5616,14 +5616,14 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1,219,865
-Cr. 121.99</t>
+          <t>1,524,832
+Cr. 152.48</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1,210,396
-Cr. 121.04</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -5634,36 +5634,36 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>1,292,908
-Cr. 129.29</t>
+          <t>1,616,135
+Cr. 161.61</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1,415,222
-Cr. 141.52</t>
+          <t>1,504,723
+Cr. 150.47</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>122,314
-Cr. 12.23</t>
+          <t>-111,412
+Cr. -11.14</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>204,826
-Cr. 20.48</t>
+          <t>1,504,723
+Cr. 150.47</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -5681,14 +5681,14 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>51,542
-Cr. 5.15</t>
+          <t>64,427
+Cr. 6.44</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>25,217
-Cr. 2.52</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -5699,36 +5699,36 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>31,758
-Cr. 3.18</t>
+          <t>39,697
+Cr. 3.97</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>65,408
-Cr. 6.54</t>
+          <t>66,726
+Cr. 6.67</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>33,650
-Cr. 3.37</t>
+          <t>27,029
+Cr. 2.70</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>168</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>40,191
-Cr. 4.02</t>
+          <t>66,726
+Cr. 6.67</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -5746,14 +5746,14 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>1,258,599
-Cr. 125.86</t>
+          <t>1,573,248
+Cr. 157.32</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>1,584,718
-Cr. 158.47</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -5764,36 +5764,36 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>1,084,770
-Cr. 108.48</t>
+          <t>1,355,962
+Cr. 135.60</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1,686,251
-Cr. 168.63</t>
+          <t>1,822,494
+Cr. 182.25</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>601,481
-Cr. 60.15</t>
+          <t>466,532
+Cr. 46.65</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>101,533
-Cr. 10.15</t>
+          <t>1,822,494
+Cr. 182.25</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -5811,14 +5811,14 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>1,130,493
-Cr. 113.05</t>
+          <t>1,413,117
+Cr. 141.31</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>980,440
-Cr. 98.04</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -5829,8 +5829,8 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>875,147
-Cr. 87.51</t>
+          <t>1,093,933
+Cr. 109.39</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -5841,19 +5841,19 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>-182,913
-Cr. -18.29</t>
+          <t>-401,699
+Cr. -40.17</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>-288,206
-Cr. -28.82</t>
+          <t>692,234
+Cr. 69.22</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -5876,14 +5876,14 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>67,941
-Cr. 6.79</t>
+          <t>84,926
+Cr. 8.49</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>51,519
-Cr. 5.15</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5894,8 +5894,8 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>51,849
-Cr. 5.18</t>
+          <t>64,812
+Cr. 6.48</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -5906,19 +5906,19 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>-34,434
-Cr. -3.44</t>
+          <t>-47,397
+Cr. -4.74</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>-34,104
-Cr. -3.41</t>
+          <t>17,415
+Cr. 1.74</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -5941,14 +5941,14 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>53,675
-Cr. 5.37</t>
+          <t>67,094
+Cr. 6.71</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>38,116
-Cr. 3.81</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -5959,8 +5959,8 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>31,943
-Cr. 3.19</t>
+          <t>39,929
+Cr. 3.99</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -5971,19 +5971,19 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>12,517
-Cr. 1.25</t>
+          <t>4,531
+Cr. 0.45</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>111</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>6,344
-Cr. 0.63</t>
+          <t>44,460
+Cr. 4.45</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -6006,13 +6006,13 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>27
+          <t>33
 Cr. 0.00</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>16
+          <t>0
 Cr. 0.00</t>
         </is>
       </c>
@@ -6042,12 +6042,12 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>7
+          <t>23
 Cr. 0.00</t>
         </is>
       </c>
@@ -6071,14 +6071,14 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>4,181
-Cr. 0.42</t>
+          <t>5,226
+Cr. 0.52</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>7,971
-Cr. 0.80</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -6089,36 +6089,36 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>8,627
-Cr. 0.86</t>
+          <t>10,784
+Cr. 1.08</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>4,774
-Cr. 0.48</t>
+          <t>5,328
+Cr. 0.53</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>-3,853
-Cr. -0.39</t>
+          <t>-5,456
+Cr. -0.55</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>-3,197
-Cr. -0.32</t>
+          <t>5,328
+Cr. 0.53</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -6136,14 +6136,14 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>2,877
-Cr. 0.29</t>
+          <t>3,596
+Cr. 0.36</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3,236
-Cr. 0.32</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6154,36 +6154,36 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>4,002
-Cr. 0.40</t>
+          <t>5,002
+Cr. 0.50</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2,298
-Cr. 0.23</t>
+          <t>2,573
+Cr. 0.26</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>-1,704
-Cr. -0.17</t>
+          <t>-2,429
+Cr. -0.24</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>-938
-Cr. -0.09</t>
+          <t>2,573
+Cr. 0.26</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -6201,14 +6201,14 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>7,459
-Cr. 0.75</t>
+          <t>9,324
+Cr. 0.93</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>10,815
-Cr. 1.08</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -6219,8 +6219,8 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>3,863
-Cr. 0.39</t>
+          <t>4,829
+Cr. 0.48</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -6231,19 +6231,19 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>220,886
-Cr. 22.09</t>
+          <t>219,920
+Cr. 21.99</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>213,934
-Cr. 21.39</t>
+          <t>224,749
+Cr. 22.47</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>263
+          <t>329
 Cr. 0.03</t>
         </is>
       </c>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>181
+          <t>227
 Cr. 0.02</t>
         </is>
       </c>
@@ -6296,13 +6296,13 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>6,201
+          <t>6,155
 Cr. 0.62</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6396,54 +6396,54 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>67
+          <t>83
 Cr. 0.01</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>0
+Cr. 0.00</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>614
 Cr. 0.06</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>614
-Cr. 0.06</t>
-        </is>
-      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>205
-Cr. 0.02</t>
+          <t>256
+Cr. 0.03</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1,140
-Cr. 0.11</t>
+          <t>1,704
+Cr. 0.17</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>935
-Cr. 0.09</t>
+          <t>1,448
+Cr. 0.14</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>666</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>526
-Cr. 0.05</t>
+          <t>1,704
+Cr. 0.17</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>278</t>
         </is>
       </c>
     </row>
@@ -6461,14 +6461,14 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>1,636,547
-Cr. 163.65</t>
+          <t>2,045,684
+Cr. 204.57</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>1,793,435
-Cr. 179.34</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -6479,8 +6479,8 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>1,567,785
-Cr. 156.78</t>
+          <t>1,959,732
+Cr. 195.97</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -6491,19 +6491,19 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>735,421
-Cr. 73.54</t>
+          <t>343,474
+Cr. 34.35</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>118</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>509,771
-Cr. 50.98</t>
+          <t>2,303,206
+Cr. 230.32</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -6526,14 +6526,14 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>5,151
-Cr. 0.52</t>
+          <t>6,439
+Cr. 0.64</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3,745
-Cr. 0.37</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6544,36 +6544,36 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>10,776
-Cr. 1.08</t>
+          <t>13,470
+Cr. 1.35</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>32,998
-Cr. 3.30</t>
+          <t>37,201
+Cr. 3.72</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>22,222
-Cr. 2.22</t>
+          <t>23,731
+Cr. 2.37</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>29,253
-Cr. 2.93</t>
+          <t>37,201
+Cr. 3.72</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -6591,14 +6591,14 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>5,153
-Cr. 0.52</t>
+          <t>6,441
+Cr. 0.64</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>3,744
-Cr. 0.37</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -6609,36 +6609,36 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>10,644
-Cr. 1.06</t>
+          <t>13,305
+Cr. 1.33</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>32,998
-Cr. 3.30</t>
+          <t>37,201
+Cr. 3.72</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>22,354
-Cr. 2.24</t>
+          <t>23,896
+Cr. 2.39</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>29,254
-Cr. 2.93</t>
+          <t>37,201
+Cr. 3.72</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>117</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>1
+          <t>2
 Cr. 0.00</t>
         </is>
       </c>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>-1
+          <t>-2
 Cr. -0.00</t>
         </is>
       </c>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>5,178
-Cr. 0.52</t>
+          <t>6,472
+Cr. 0.65</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>6,345
-Cr. 0.63</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -6739,36 +6739,36 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>8,699
-Cr. 0.87</t>
+          <t>10,874
+Cr. 1.09</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>36,849
-Cr. 3.68</t>
+          <t>41,871
+Cr. 4.19</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>28,150
-Cr. 2.81</t>
+          <t>30,997
+Cr. 3.10</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>385</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>30,504
-Cr. 3.05</t>
+          <t>41,871
+Cr. 4.19</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -6786,14 +6786,14 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>-398,120
-Cr. -39.81</t>
+          <t>-497,650
+Cr. -49.77</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>-446,430
-Cr. -44.64</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -6804,36 +6804,36 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>-550,940
-Cr. -55.09</t>
+          <t>-688,675
+Cr. -68.87</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-481,299
-Cr. -48.13</t>
+          <t>-623,356
+Cr. -62.34</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>69,641
-Cr. 6.96</t>
+          <t>65,319
+Cr. 6.53</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-34,869
-Cr. -3.49</t>
+          <t>-623,356
+Cr. -62.34</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -6851,14 +6851,14 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>385,800
-Cr. 38.58</t>
+          <t>482,250
+Cr. 48.23</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>2,128,535
-Cr. 212.85</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -6869,36 +6869,36 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>599,193
-Cr. 59.92</t>
+          <t>748,991
+Cr. 74.90</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>2,101,259
-Cr. 210.13</t>
+          <t>2,269,838
+Cr. 226.98</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>1,502,066
-Cr. 150.21</t>
+          <t>1,520,847
+Cr. 152.08</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>-27,276
-Cr. -2.73</t>
+          <t>2,269,838
+Cr. 226.98</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>11,717,125
-Cr. 1171.71</t>
+          <t>14,646,406
+Cr. 1464.64</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>13,886,868
-Cr. 1388.69</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -6934,36 +6934,36 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>10,860,943
-Cr. 1086.09</t>
+          <t>13,576,178
+Cr. 1357.62</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>15,263,467
-Cr. 1526.35</t>
+          <t>16,996,095
+Cr. 1699.61</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>4,402,524
-Cr. 440.25</t>
+          <t>3,419,917
+Cr. 341.99</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1,376,599
-Cr. 137.66</t>
+          <t>16,996,095
+Cr. 1699.61</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -6986,20 +6986,20 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - JUL 2026 | uploaded 2026-08-31T12:33:38+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -7068,14 +7068,14 @@
         <is>
           <t>B
 Previous Budget Proportion
-A / 12 * 4</t>
+A / 12 * 5</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>C
 Previous Actual Expenditure
-Upto JUL 2025</t>
+up to AUG 2025</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -7089,14 +7089,14 @@
         <is>
           <t>E
 Current Budget Proportion
-D / 12 * 4</t>
+D / 12 * 5</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>F
 Current Actual Expenditure
-Upto JUL 2026</t>
+up to AUG 2026</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -7147,14 +7147,14 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>221,876
-Cr. 22.19</t>
+          <t>277,345
+Cr. 27.73</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>215,548
-Cr. 21.55</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -7165,36 +7165,36 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>213,841
-Cr. 21.38</t>
+          <t>267,301
+Cr. 26.73</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>236,563
-Cr. 23.66</t>
+          <t>294,025
+Cr. 29.40</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>22,722
-Cr. 2.27</t>
+          <t>26,724
+Cr. 2.67</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>21,015
-Cr. 2.10</t>
+          <t>294,025
+Cr. 29.40</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -7217,14 +7217,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,282,548
-Cr. 128.25</t>
+          <t>1,603,185
+Cr. 160.32</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,313,794
-Cr. 131.38</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -7235,36 +7235,36 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1,202,967
-Cr. 120.30</t>
+          <t>1,503,709
+Cr. 150.37</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1,473,830
-Cr. 147.38</t>
+          <t>1,779,391
+Cr. 177.94</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>270,863
-Cr. 27.09</t>
+          <t>275,682
+Cr. 27.57</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>118</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>160,036
-Cr. 16.00</t>
+          <t>1,779,391
+Cr. 177.94</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -7287,14 +7287,14 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>696,871
-Cr. 69.69</t>
+          <t>871,088
+Cr. 87.11</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>992,115
-Cr. 99.21</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -7305,8 +7305,8 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>621,614
-Cr. 62.16</t>
+          <t>777,018
+Cr. 77.70</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -7317,19 +7317,19 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>160,418
-Cr. 16.04</t>
+          <t>5,014
+Cr. 0.50</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>-210,083
-Cr. -21.01</t>
+          <t>782,032
+Cr. 78.20</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>498,058
-Cr. 49.81</t>
+          <t>622,572
+Cr. 62.26</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>510,355
-Cr. 51.04</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -7375,36 +7375,36 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>451,194
-Cr. 45.12</t>
+          <t>563,992
+Cr. 56.40</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>765,060
-Cr. 76.51</t>
+          <t>882,061
+Cr. 88.21</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>313,866
-Cr. 31.39</t>
+          <t>318,069
+Cr. 31.81</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>254,705
-Cr. 25.47</t>
+          <t>882,061
+Cr. 88.21</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -7427,14 +7427,14 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>738,232
-Cr. 73.82</t>
+          <t>922,790
+Cr. 92.28</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>680,262
-Cr. 68.03</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -7445,36 +7445,36 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>686,650
-Cr. 68.67</t>
+          <t>858,312
+Cr. 85.83</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>838,163
-Cr. 83.82</t>
+          <t>987,240
+Cr. 98.72</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>151,513
-Cr. 15.15</t>
+          <t>128,928
+Cr. 12.89</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>157,901
-Cr. 15.79</t>
+          <t>987,240
+Cr. 98.72</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -7497,14 +7497,14 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1,311,347
-Cr. 131.13</t>
+          <t>1,639,183
+Cr. 163.92</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,252,980
-Cr. 125.30</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -7515,36 +7515,36 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1,117,522
-Cr. 111.75</t>
+          <t>1,396,902
+Cr. 139.69</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,617,389
-Cr. 161.74</t>
+          <t>1,953,133
+Cr. 195.31</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>499,867
-Cr. 49.99</t>
+          <t>556,230
+Cr. 55.62</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>364,409
-Cr. 36.44</t>
+          <t>1,953,133
+Cr. 195.31</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -7567,14 +7567,14 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1,660,619
-Cr. 166.06</t>
+          <t>2,075,774
+Cr. 207.58</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1,637,160
-Cr. 163.72</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -7585,36 +7585,36 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1,476,255
-Cr. 147.63</t>
+          <t>1,845,319
+Cr. 184.53</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1,782,151
-Cr. 178.22</t>
+          <t>2,193,589
+Cr. 219.36</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>305,896
-Cr. 30.59</t>
+          <t>348,270
+Cr. 34.83</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>119</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>144,991
-Cr. 14.50</t>
+          <t>2,193,589
+Cr. 219.36</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -7637,14 +7637,14 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>4,255,518
-Cr. 425.55</t>
+          <t>5,319,397
+Cr. 531.94</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4,179,746
-Cr. 417.97</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -7655,31 +7655,31 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>3,869,069
-Cr. 386.91</t>
+          <t>4,836,336
+Cr. 483.63</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>4,605,644
-Cr. 460.56</t>
+          <t>4,657,805
+Cr. 465.78</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>736,575
-Cr. 73.66</t>
+          <t>-178,531
+Cr. -17.85</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>425,898
-Cr. 42.59</t>
+          <t>4,657,805
+Cr. 465.78</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -7707,14 +7707,14 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>417,282
-Cr. 41.73</t>
+          <t>521,603
+Cr. 52.16</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>744,311
-Cr. 74.43</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -7725,36 +7725,36 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>464,277
-Cr. 46.43</t>
+          <t>580,347
+Cr. 58.03</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>810,746
-Cr. 81.07</t>
+          <t>915,761
+Cr. 91.58</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>346,469
-Cr. 34.65</t>
+          <t>335,414
+Cr. 33.54</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>158</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>66,435
-Cr. 6.64</t>
+          <t>915,761
+Cr. 91.58</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -7777,14 +7777,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>330,612
-Cr. 33.06</t>
+          <t>413,265
+Cr. 41.33</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>324,212
-Cr. 32.42</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -7795,36 +7795,36 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>331,546
-Cr. 33.15</t>
+          <t>414,432
+Cr. 41.44</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>356,769
-Cr. 35.68</t>
+          <t>439,545
+Cr. 43.95</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>25,223
-Cr. 2.52</t>
+          <t>25,112
+Cr. 2.51</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>32,557
-Cr. 3.26</t>
+          <t>439,545
+Cr. 43.95</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -7847,14 +7847,14 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>367,729
-Cr. 36.77</t>
+          <t>459,661
+Cr. 45.97</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>400,404
-Cr. 40.04</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -7865,20 +7865,20 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>430,356
-Cr. 43.04</t>
+          <t>537,945
+Cr. 53.79</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>425,677
-Cr. 42.57</t>
+          <t>532,661
+Cr. 53.27</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>-4,679
-Cr. -0.47</t>
+          <t>-5,284
+Cr. -0.53</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -7888,13 +7888,13 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25,273
-Cr. 2.53</t>
+          <t>532,661
+Cr. 53.27</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -7913,14 +7913,14 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>11,780,691
-Cr. 1178.07</t>
+          <t>14,725,864
+Cr. 1472.59</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>12,250,887
-Cr. 1225.09</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -7931,36 +7931,36 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>10,865,291
-Cr. 1086.53</t>
+          <t>13,581,614
+Cr. 1358.16</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>13,694,024
-Cr. 1369.40</t>
+          <t>15,417,243
+Cr. 1541.72</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>2,828,733
-Cr. 282.87</t>
+          <t>1,835,629
+Cr. 183.56</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>1,443,137
-Cr. 144.31</t>
+          <t>15,417,243
+Cr. 1541.72</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -7983,14 +7983,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>-63,567
-Cr. -6.36</t>
+          <t>-79,458
+Cr. -7.95</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,635,983
-Cr. 163.60</t>
+          <t>0
+Cr. 0.00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -8001,36 +8001,36 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-4,348
-Cr. -0.43</t>
+          <t>-5,435
+Cr. -0.54</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>1,569,443
-Cr. 156.94</t>
+          <t>1,578,852
+Cr. 157.89</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>1,573,791
-Cr. 157.38</t>
+          <t>1,584,287
+Cr. 158.43</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-36093</t>
+          <t>-29047</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>-66,540
-Cr. -6.65</t>
+          <t>1,578,852
+Cr. 157.89</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>-12031</t>
+          <t>-12103</t>
         </is>
       </c>
     </row>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1294,7 +1294,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2541,7 +2541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3791,7 +3791,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6999,7 +6999,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T12:16:24+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1294,7 +1294,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2541,7 +2541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3791,7 +3791,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -6999,7 +6999,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-01T16:12:23+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>

--- a/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
+++ b/exports/Current_Previous_Year_PU_Demand_Analysis.xlsx
@@ -495,7 +495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>Demand SMH Wise - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -619,14 +619,14 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>294,025
-Cr. 29.40</t>
+          <t>294,135
+Cr. 29.41</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>26,724
-Cr. 2.67</t>
+          <t>26,834
+Cr. 2.68</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -636,8 +636,8 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>347,497
-Cr. 34.75</t>
+          <t>347,387
+Cr. 34.74</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>1,779,391
-Cr. 177.94</t>
+          <t>1,781,320
+Cr. 178.13</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>275,682
-Cr. 27.57</t>
+          <t>277,611
+Cr. 27.76</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -688,8 +688,8 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1,829,511
-Cr. 182.95</t>
+          <t>1,827,582
+Cr. 182.76</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -775,30 +775,30 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>882,060
-Cr. 88.21</t>
+          <t>911,131
+Cr. 91.11</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>318,068
-Cr. 31.81</t>
+          <t>347,139
+Cr. 34.71</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>471,521
-Cr. 47.15</t>
+          <t>442,450
+Cr. 44.24</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -827,25 +827,25 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>987,240
-Cr. 98.72</t>
+          <t>995,022
+Cr. 99.50</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>128,928
-Cr. 12.89</t>
+          <t>136,710
+Cr. 13.67</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1,072,710
-Cr. 107.27</t>
+          <t>1,064,928
+Cr. 106.49</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -879,30 +879,30 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1,953,133
-Cr. 195.31</t>
+          <t>1,978,638
+Cr. 197.86</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>556,231
-Cr. 55.62</t>
+          <t>581,736
+Cr. 58.17</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,399,433
-Cr. 139.94</t>
+          <t>1,373,928
+Cr. 137.39</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -931,14 +931,14 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2,193,589
-Cr. 219.36</t>
+          <t>2,192,865
+Cr. 219.29</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>348,270
-Cr. 34.83</t>
+          <t>347,546
+Cr. 34.75</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -948,8 +948,8 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,235,177
-Cr. 223.52</t>
+          <t>2,235,901
+Cr. 223.59</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -983,30 +983,30 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>4,657,805
-Cr. 465.78</t>
+          <t>5,702,475
+Cr. 570.25</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>-178,531
-Cr. -17.85</t>
+          <t>866,139
+Cr. 86.61</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>6,949,401
-Cr. 694.94</t>
+          <t>5,904,731
+Cr. 590.47</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -1035,14 +1035,14 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>915,762
-Cr. 91.58</t>
+          <t>916,954
+Cr. 91.70</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>335,415
-Cr. 33.54</t>
+          <t>336,607
+Cr. 33.66</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1052,8 +1052,8 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>477,070
-Cr. 47.71</t>
+          <t>475,878
+Cr. 47.59</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1087,25 +1087,25 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>439,544
-Cr. 43.95</t>
+          <t>441,761
+Cr. 44.18</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>25,112
-Cr. 2.51</t>
+          <t>27,328
+Cr. 2.73</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>555,094
-Cr. 55.51</t>
+          <t>552,877
+Cr. 55.29</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1181,36 +1181,36 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>13,581,613
+          <t>13,581,614
 Cr. 1358.16</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>15,417,243
-Cr. 1541.72</t>
+          <t>16,528,995
+Cr. 1652.90</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1,835,630
-Cr. 183.56</t>
+          <t>2,947,381
+Cr. 294.74</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>17,178,630
-Cr. 1717.86</t>
+          <t>16,066,878
+Cr. 1606.69</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -1239,30 +1239,30 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1,578,852
-Cr. 157.89</t>
+          <t>1,578,052
+Cr. 157.81</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1,584,287
-Cr. 158.43</t>
+          <t>1,583,487
+Cr. 158.35</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-29050</t>
+          <t>-29033</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>-1,591,897
-Cr. -159.19</t>
+          <t>-1,591,097
+Cr. -159.11</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>-12103</t>
+          <t>-12097</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>PU Staff Current Year - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3,073,272
-Cr. 307.33</t>
+          <t>3,071,823
+Cr. 307.18</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>278,935
-Cr. 27.89</t>
+          <t>277,486
+Cr. 27.75</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1422,8 +1422,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>3,633,137
-Cr. 363.31</t>
+          <t>3,634,586
+Cr. 363.46</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1452,14 +1452,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1,968,578
-Cr. 196.86</t>
+          <t>1,966,618
+Cr. 196.66</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>260,056
-Cr. 26.01</t>
+          <t>258,096
+Cr. 25.81</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1469,8 +1469,8 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2,131,875
-Cr. 213.19</t>
+          <t>2,133,835
+Cr. 213.38</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1499,13 +1499,13 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>81
+          <t>72
 Cr. 0.01</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>-118,706
+          <t>-118,715
 Cr. -11.87</t>
         </is>
       </c>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>285,008
+          <t>285,017
 Cr. 28.50</t>
         </is>
       </c>
@@ -1546,14 +1546,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>337,922
-Cr. 33.79</t>
+          <t>337,362
+Cr. 33.74</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>14,506
-Cr. 1.45</t>
+          <t>13,946
+Cr. 1.39</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1563,13 +1563,13 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>438,276
-Cr. 43.83</t>
+          <t>438,836
+Cr. 43.88</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -1593,14 +1593,14 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>216,618
-Cr. 21.66</t>
+          <t>216,397
+Cr. 21.64</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>9,698
-Cr. 0.97</t>
+          <t>9,477
+Cr. 0.95</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1610,8 +1610,8 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>279,991
-Cr. 28.00</t>
+          <t>280,212
+Cr. 28.02</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1781,13 +1781,13 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>122,506
+          <t>122,492
 Cr. 12.25</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>35,042
+          <t>35,028
 Cr. 3.50</t>
         </is>
       </c>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>87,407
+          <t>87,421
 Cr. 8.74</t>
         </is>
       </c>
@@ -1828,14 +1828,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>279,175
-Cr. 27.92</t>
+          <t>278,899
+Cr. 27.89</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>59,245
-Cr. 5.92</t>
+          <t>58,969
+Cr. 5.90</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1845,8 +1845,8 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>248,657
-Cr. 24.87</t>
+          <t>248,933
+Cr. 24.89</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1875,13 +1875,13 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>427
+          <t>428
 Cr. 0.04</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>-1,059
+          <t>-1,058
 Cr. -0.11</t>
         </is>
       </c>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>3,139
+          <t>3,138
 Cr. 0.31</t>
         </is>
       </c>
@@ -1969,14 +1969,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>217,182
-Cr. 21.72</t>
+          <t>217,100
+Cr. 21.71</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>88,815
-Cr. 8.88</t>
+          <t>88,733
+Cr. 8.87</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1986,8 +1986,8 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>90,899
-Cr. 9.09</t>
+          <t>90,981
+Cr. 9.10</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2063,30 +2063,30 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>12,682
-Cr. 1.27</t>
+          <t>12,259
+Cr. 1.23</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>4,922
-Cr. 0.49</t>
+          <t>4,499
+Cr. 0.45</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>158</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>5,941
-Cr. 0.59</t>
+          <t>6,364
+Cr. 0.64</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>374,892
-Cr. 37.49</t>
+          <t>375,011
+Cr. 37.50</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>216,801
-Cr. 21.68</t>
+          <t>216,920
+Cr. 21.69</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2127,8 +2127,8 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>4,526
-Cr. 0.45</t>
+          <t>4,407
+Cr. 0.44</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2157,25 +2157,25 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>152,898
-Cr. 15.29</t>
+          <t>154,029
+Cr. 15.40</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>-7,265
-Cr. -0.73</t>
+          <t>-6,134
+Cr. -0.61</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>231,494
-Cr. 23.15</t>
+          <t>230,363
+Cr. 23.04</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2298,25 +2298,25 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>5,329
-Cr. 0.53</t>
+          <t>5,394
+Cr. 0.54</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>-5,455
-Cr. -0.55</t>
+          <t>-5,390
+Cr. -0.54</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>20,553
-Cr. 2.06</t>
+          <t>20,488
+Cr. 2.05</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2345,13 +2345,13 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>2,572
+          <t>2,574
 Cr. 0.26</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>-2,430
+          <t>-2,428
 Cr. -0.24</t>
         </is>
       </c>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>9,433
+          <t>9,431
 Cr. 0.94</t>
         </is>
       </c>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>7,958,493
-Cr. 795.85</t>
+          <t>7,954,817
+Cr. 795.48</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>1,163,693
-Cr. 116.37</t>
+          <t>1,160,017
+Cr. 116.00</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2503,8 +2503,8 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>8,349,027
-Cr. 834.90</t>
+          <t>8,352,703
+Cr. 835.27</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2531,7 +2531,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -2541,7 +2541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>PU Non Staff Current Year - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -2934,30 +2934,30 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>746,612
-Cr. 74.66</t>
+          <t>860,139
+Cr. 86.01</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>301,299
-Cr. 30.13</t>
+          <t>414,826
+Cr. 41.48</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>322,140
-Cr. 32.21</t>
+          <t>208,613
+Cr. 20.86</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -2981,13 +2981,13 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>70,596
+          <t>70,608
 Cr. 7.06</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>8,118
+          <t>8,130
 Cr. 0.81</t>
         </is>
       </c>
@@ -2998,8 +2998,8 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>79,351
-Cr. 7.94</t>
+          <t>79,339
+Cr. 7.93</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -3028,30 +3028,30 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1,504,722
-Cr. 150.47</t>
+          <t>1,916,509
+Cr. 191.65</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>-111,413
-Cr. -11.14</t>
+          <t>300,374
+Cr. 30.04</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2,374,002
-Cr. 237.40</t>
+          <t>1,962,215
+Cr. 196.22</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -3075,30 +3075,30 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>66,725
-Cr. 6.67</t>
+          <t>81,636
+Cr. 8.16</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>27,028
-Cr. 2.70</t>
+          <t>41,939
+Cr. 4.19</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>206</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>28,548
-Cr. 2.85</t>
+          <t>13,637
+Cr. 1.36</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -3122,25 +3122,25 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1,822,493
-Cr. 182.25</t>
+          <t>1,824,117
+Cr. 182.41</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>466,531
-Cr. 46.65</t>
+          <t>468,154
+Cr. 46.82</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1,431,817
-Cr. 143.18</t>
+          <t>1,430,193
+Cr. 143.02</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3169,30 +3169,30 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>692,235
-Cr. 69.22</t>
+          <t>834,970
+Cr. 83.50</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>-401,698
-Cr. -40.17</t>
+          <t>-258,963
+Cr. -25.90</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1,933,205
-Cr. 193.32</t>
+          <t>1,790,470
+Cr. 179.05</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -3216,30 +3216,30 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>17,414
-Cr. 1.74</t>
+          <t>23,732
+Cr. 2.37</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-47,398
-Cr. -4.74</t>
+          <t>-41,080
+Cr. -4.11</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>138,134
-Cr. 13.81</t>
+          <t>131,816
+Cr. 13.18</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -3263,30 +3263,30 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>44,460
-Cr. 4.45</t>
+          <t>56,334
+Cr. 5.63</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>4,531
-Cr. 0.45</t>
+          <t>16,405
+Cr. 1.64</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>51,369
-Cr. 5.14</t>
+          <t>39,495
+Cr. 3.95</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3404,30 +3404,30 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2,303,206
-Cr. 230.32</t>
+          <t>2,715,415
+Cr. 271.54</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>343,474
-Cr. 34.35</t>
+          <t>755,683
+Cr. 75.57</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2,400,150
-Cr. 240.01</t>
+          <t>1,987,941
+Cr. 198.79</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -3451,30 +3451,30 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>37,201
-Cr. 3.72</t>
+          <t>37,406
+Cr. 3.74</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>23,731
-Cr. 2.37</t>
+          <t>23,936
+Cr. 2.39</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>-4,872
-Cr. -0.49</t>
+          <t>-5,077
+Cr. -0.51</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -3498,25 +3498,25 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>37,201
-Cr. 3.72</t>
+          <t>37,406
+Cr. 3.74</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>23,896
-Cr. 2.39</t>
+          <t>24,101
+Cr. 2.41</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-5,269
-Cr. -0.53</t>
+          <t>-5,474
+Cr. -0.55</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3592,13 +3592,13 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>41,871
+          <t>41,893
 Cr. 4.19</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>30,997
+          <t>31,019
 Cr. 3.10</t>
         </is>
       </c>
@@ -3609,13 +3609,13 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-15,773
+          <t>-15,795
 Cr. -1.58</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -3639,30 +3639,30 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>-623,357
-Cr. -62.34</t>
+          <t>-592,130
+Cr. -59.21</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>65,318
-Cr. 6.53</t>
+          <t>96,545
+Cr. 9.65</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>-1,029,464
-Cr. -102.95</t>
+          <t>-1,060,691
+Cr. -106.07</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -3686,30 +3686,30 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2,269,838
-Cr. 226.98</t>
+          <t>2,237,813
+Cr. 223.78</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>1,520,847
-Cr. 152.08</t>
+          <t>1,488,822
+Cr. 148.88</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>299</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-472,259
-Cr. -47.23</t>
+          <t>-440,234
+Cr. -44.02</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -3727,36 +3727,36 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>6,781,379
+          <t>6,781,378
 Cr. 678.14</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>9,037,599
-Cr. 903.76</t>
+          <t>10,152,230
+Cr. 1015.22</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2,256,220
-Cr. 225.62</t>
+          <t>3,370,852
+Cr. 337.09</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>7,237,709
-Cr. 723.77</t>
+          <t>6,123,078
+Cr. 612.31</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -3778,20 +3778,20 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>PU Previous Year Comparison - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3932,8 +3932,8 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>3,038,266
+Cr. 303.83</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -3950,14 +3950,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>3,073,271
-Cr. 307.33</t>
+          <t>3,071,823
+Cr. 307.18</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>278,934
-Cr. 27.89</t>
+          <t>277,486
+Cr. 27.75</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -3967,8 +3967,8 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>3,073,271
-Cr. 307.33</t>
+          <t>33,557
+Cr. 3.36</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3997,8 +3997,8 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>1,789,595
+Cr. 178.96</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1,968,578
-Cr. 196.86</t>
+          <t>1,966,618
+Cr. 196.66</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>260,056
-Cr. 26.01</t>
+          <t>258,096
+Cr. 25.81</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -4032,8 +4032,8 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>1,968,578
-Cr. 196.86</t>
+          <t>177,023
+Cr. 17.70</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -4062,8 +4062,8 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>226
+Cr. 0.02</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -4080,13 +4080,13 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>82
+          <t>72
 Cr. 0.01</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>-118,705
+          <t>-118,715
 Cr. -11.87</t>
         </is>
       </c>
@@ -4097,8 +4097,8 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>82
-Cr. 0.01</t>
+          <t>-154
+Cr. -0.02</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -4127,8 +4127,8 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>332,414
+Cr. 33.24</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>337,922
-Cr. 33.79</t>
+          <t>337,362
+Cr. 33.74</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>14,506
-Cr. 1.45</t>
+          <t>13,946
+Cr. 1.39</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -4162,13 +4162,13 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>337,922
-Cr. 33.79</t>
+          <t>4,948
+Cr. 0.49</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -4192,8 +4192,8 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>209,713
+Cr. 20.97</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>216,617
-Cr. 21.66</t>
+          <t>216,397
+Cr. 21.64</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>9,697
-Cr. 0.97</t>
+          <t>9,477
+Cr. 0.95</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -4227,8 +4227,8 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>216,617
-Cr. 21.66</t>
+          <t>6,684
+Cr. 0.67</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -4257,8 +4257,8 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>500,022
+Cr. 50.00</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -4275,13 +4275,13 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>532,039
+          <t>532,040
 Cr. 53.20</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>-3,456
+          <t>-3,455
 Cr. -0.35</t>
         </is>
       </c>
@@ -4292,8 +4292,8 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>532,039
-Cr. 53.20</t>
+          <t>32,018
+Cr. 3.20</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -4322,8 +4322,8 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>328,323
+Cr. 32.83</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -4357,8 +4357,8 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>364,653
-Cr. 36.47</t>
+          <t>36,330
+Cr. 3.63</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -4387,8 +4387,8 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>67,517
+Cr. 6.75</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -4422,8 +4422,8 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>59,582
-Cr. 5.96</t>
+          <t>-7,935
+Cr. -0.79</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -4452,8 +4452,8 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>117,681
+Cr. 11.77</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -4470,13 +4470,13 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>122,506
+          <t>122,492
 Cr. 12.25</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>35,042
+          <t>35,028
 Cr. 3.50</t>
         </is>
       </c>
@@ -4487,8 +4487,8 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>122,506
-Cr. 12.25</t>
+          <t>4,811
+Cr. 0.48</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -4517,8 +4517,8 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>282,709
+Cr. 28.27</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -4535,14 +4535,14 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>279,175
-Cr. 27.92</t>
+          <t>278,899
+Cr. 27.89</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>59,245
-Cr. 5.92</t>
+          <t>58,969
+Cr. 5.90</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -4552,8 +4552,8 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>279,175
-Cr. 27.92</t>
+          <t>-3,810
+Cr. -0.38</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -4582,8 +4582,8 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>378
+Cr. 0.04</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -4600,13 +4600,13 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>426
+          <t>428
 Cr. 0.04</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>-1,060
+          <t>-1,058
 Cr. -0.11</t>
         </is>
       </c>
@@ -4617,8 +4617,8 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>426
-Cr. 0.04</t>
+          <t>50
+Cr. 0.01</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -4647,8 +4647,8 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>12,161
+Cr. 1.22</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -4682,8 +4682,8 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>11,132
-Cr. 1.11</t>
+          <t>-1,029
+Cr. -0.10</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -4712,8 +4712,8 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>209,161
+Cr. 20.92</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>217,183
-Cr. 21.72</t>
+          <t>217,100
+Cr. 21.71</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>88,816
-Cr. 8.88</t>
+          <t>88,733
+Cr. 8.87</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4747,8 +4747,8 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>217,183
-Cr. 21.72</t>
+          <t>7,939
+Cr. 0.79</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -4972,8 +4972,8 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>7,125
+Cr. 0.71</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -4990,30 +4990,30 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>12,682
-Cr. 1.27</t>
+          <t>12,259
+Cr. 1.23</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>4,922
-Cr. 0.49</t>
+          <t>4,499
+Cr. 0.45</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>158</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>12,682
-Cr. 1.27</t>
+          <t>5,134
+Cr. 0.51</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -5297,8 +5297,8 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>363,237
+Cr. 36.32</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -5315,14 +5315,14 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>374,893
-Cr. 37.49</t>
+          <t>375,011
+Cr. 37.50</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>216,802
-Cr. 21.68</t>
+          <t>216,920
+Cr. 21.69</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -5332,8 +5332,8 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>374,893
-Cr. 37.49</t>
+          <t>11,774
+Cr. 1.18</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -5362,8 +5362,8 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>160,765
+Cr. 16.08</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -5380,25 +5380,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>152,897
-Cr. 15.29</t>
+          <t>154,029
+Cr. 15.40</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>-7,266
-Cr. -0.73</t>
+          <t>-6,134
+Cr. -0.61</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>152,897
-Cr. 15.29</t>
+          <t>-6,736
+Cr. -0.67</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -5427,8 +5427,8 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>516,298
+Cr. 51.63</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -5445,30 +5445,30 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>746,612
-Cr. 74.66</t>
+          <t>860,139
+Cr. 86.01</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>301,299
-Cr. 30.13</t>
+          <t>414,826
+Cr. 41.48</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>193</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>746,612
-Cr. 74.66</t>
+          <t>343,841
+Cr. 34.38</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -5492,8 +5492,8 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>105,637
+Cr. 10.56</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -5510,13 +5510,13 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>70,597
+          <t>70,608
 Cr. 7.06</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>8,119
+          <t>8,130
 Cr. 0.81</t>
         </is>
       </c>
@@ -5527,8 +5527,8 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>70,597
-Cr. 7.06</t>
+          <t>-35,029
+Cr. -3.50</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>0
+          <t>5
 Cr. 0.00</t>
         </is>
       </c>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>476
+          <t>471
 Cr. 0.05</t>
         </is>
       </c>
@@ -5622,8 +5622,8 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>1,673,871
+Cr. 167.39</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -5640,30 +5640,30 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1,504,723
-Cr. 150.47</t>
+          <t>1,916,509
+Cr. 191.65</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>-111,412
-Cr. -11.14</t>
+          <t>300,374
+Cr. 30.04</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>119</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1,504,723
-Cr. 150.47</t>
+          <t>242,638
+Cr. 24.26</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -5687,8 +5687,8 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>30,020
+Cr. 3.00</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -5705,30 +5705,30 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>66,726
-Cr. 6.67</t>
+          <t>81,636
+Cr. 8.16</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>27,029
-Cr. 2.70</t>
+          <t>41,939
+Cr. 4.19</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>66,726
-Cr. 6.67</t>
+          <t>51,616
+Cr. 5.16</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -5752,8 +5752,8 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>1,712,812
+Cr. 171.28</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -5770,25 +5770,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1,822,494
-Cr. 182.25</t>
+          <t>1,824,117
+Cr. 182.41</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>466,532
-Cr. 46.65</t>
+          <t>468,154
+Cr. 46.82</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1,822,494
-Cr. 182.25</t>
+          <t>111,305
+Cr. 11.13</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -5817,8 +5817,8 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>1,232,129
+Cr. 123.21</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -5835,30 +5835,30 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>692,234
-Cr. 69.22</t>
+          <t>834,970
+Cr. 83.50</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>-401,699
-Cr. -40.17</t>
+          <t>-258,963
+Cr. -25.90</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>692,234
-Cr. 69.22</t>
+          <t>-397,159
+Cr. -39.72</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -5882,8 +5882,8 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>66,517
+Cr. 6.65</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5900,30 +5900,30 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>17,415
-Cr. 1.74</t>
+          <t>23,732
+Cr. 2.37</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>-47,397
-Cr. -4.74</t>
+          <t>-41,080
+Cr. -4.11</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>17,415
-Cr. 1.74</t>
+          <t>-42,785
+Cr. -4.28</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -5947,8 +5947,8 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>48,808
+Cr. 4.88</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -5965,30 +5965,30 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>44,460
-Cr. 4.45</t>
+          <t>56,334
+Cr. 5.63</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>4,531
-Cr. 0.45</t>
+          <t>16,405
+Cr. 1.64</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>141</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>44,460
-Cr. 4.45</t>
+          <t>7,526
+Cr. 0.75</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0
+          <t>30
 Cr. 0.00</t>
         </is>
       </c>
@@ -6047,8 +6047,8 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>23
-Cr. 0.00</t>
+          <t>-7
+Cr. -0.00</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -6077,8 +6077,8 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>9,795
+Cr. 0.98</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -6095,25 +6095,25 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>5,328
-Cr. 0.53</t>
+          <t>5,394
+Cr. 0.54</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>-5,456
-Cr. -0.55</t>
+          <t>-5,390
+Cr. -0.54</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>5,328
-Cr. 0.53</t>
+          <t>-4,401
+Cr. -0.44</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -6142,8 +6142,8 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>3,954
+Cr. 0.40</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -6160,13 +6160,13 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2,573
+          <t>2,574
 Cr. 0.26</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>-2,429
+          <t>-2,428
 Cr. -0.24</t>
         </is>
       </c>
@@ -6177,8 +6177,8 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2,573
-Cr. 0.26</t>
+          <t>-1,380
+Cr. -0.14</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -6207,8 +6207,8 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>11,300
+Cr. 1.13</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -6225,13 +6225,13 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>224,749
+          <t>224,748
 Cr. 22.47</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>219,920
+          <t>219,919
 Cr. 21.99</t>
         </is>
       </c>
@@ -6242,8 +6242,8 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>224,749
-Cr. 22.47</t>
+          <t>213,448
+Cr. 21.34</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -6402,8 +6402,8 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>726
+Cr. 0.07</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6420,13 +6420,13 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1,704
+          <t>1,705
 Cr. 0.17</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>1,448
+          <t>1,449
 Cr. 0.14</t>
         </is>
       </c>
@@ -6437,8 +6437,8 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1,704
-Cr. 0.17</t>
+          <t>979
+Cr. 0.10</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -6467,8 +6467,8 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>2,223,473
+Cr. 222.35</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -6485,30 +6485,30 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>2,303,206
-Cr. 230.32</t>
+          <t>2,715,415
+Cr. 271.54</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>343,474
-Cr. 34.35</t>
+          <t>755,683
+Cr. 75.57</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>139</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>2,303,206
-Cr. 230.32</t>
+          <t>491,942
+Cr. 49.19</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -6532,8 +6532,8 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>6,397
+Cr. 0.64</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -6550,30 +6550,30 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>37,201
-Cr. 3.72</t>
+          <t>37,406
+Cr. 3.74</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>23,731
-Cr. 2.37</t>
+          <t>23,936
+Cr. 2.39</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>37,201
-Cr. 3.72</t>
+          <t>31,009
+Cr. 3.10</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -6597,8 +6597,8 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>6,396
+Cr. 0.64</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -6615,25 +6615,25 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>37,201
-Cr. 3.72</t>
+          <t>37,406
+Cr. 3.74</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>23,896
-Cr. 2.39</t>
+          <t>24,101
+Cr. 2.41</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>37,201
-Cr. 3.72</t>
+          <t>31,010
+Cr. 3.10</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -6727,8 +6727,8 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>8,428
+Cr. 0.84</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -6745,13 +6745,13 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>41,871
+          <t>41,893
 Cr. 4.19</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>30,997
+          <t>31,019
 Cr. 3.10</t>
         </is>
       </c>
@@ -6762,13 +6762,13 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>41,871
-Cr. 4.19</t>
+          <t>33,465
+Cr. 3.35</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -6792,8 +6792,8 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>-533,141
+Cr. -53.31</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -6810,30 +6810,30 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-623,356
-Cr. -62.34</t>
+          <t>-592,130
+Cr. -59.21</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>65,319
-Cr. 6.53</t>
+          <t>96,545
+Cr. 9.65</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-623,356
-Cr. -62.34</t>
+          <t>-58,989
+Cr. -5.90</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -6857,8 +6857,8 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>2,253,377
+Cr. 225.34</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -6875,30 +6875,30 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>2,269,838
-Cr. 226.98</t>
+          <t>2,237,813
+Cr. 223.78</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>1,520,847
-Cr. 152.08</t>
+          <t>1,488,822
+Cr. 148.88</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>2,269,838
-Cr. 226.98</t>
+          <t>-15,564
+Cr. -1.56</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -6922,8 +6922,8 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>16,796,125
+Cr. 1679.61</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -6940,30 +6940,30 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>16,996,095
-Cr. 1699.61</t>
+          <t>18,107,047
+Cr. 1810.70</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>3,419,917
-Cr. 341.99</t>
+          <t>4,530,869
+Cr. 453.09</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>16,996,095
-Cr. 1699.61</t>
+          <t>1,310,922
+Cr. 131.09</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -6986,20 +6986,20 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-03T13:15:58+05:30</t>
+          <t>Demand Previous Year Comparison - AUG 2026 | uploaded 2026-09-05T18:02:11+05:30</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -7153,8 +7153,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>267,838
+Cr. 26.78</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -7171,14 +7171,14 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>294,025
-Cr. 29.40</t>
+          <t>294,135
+Cr. 29.41</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>26,724
-Cr. 2.67</t>
+          <t>26,834
+Cr. 2.68</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -7188,8 +7188,8 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>294,025
-Cr. 29.40</t>
+          <t>26,297
+Cr. 2.63</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -7223,8 +7223,8 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>1,635,185
+Cr. 163.52</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -7241,14 +7241,14 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1,779,391
-Cr. 177.94</t>
+          <t>1,781,320
+Cr. 178.13</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>275,682
-Cr. 27.57</t>
+          <t>277,611
+Cr. 27.76</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -7258,8 +7258,8 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>1,779,391
-Cr. 177.94</t>
+          <t>146,135
+Cr. 14.61</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -7293,8 +7293,8 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>995,067
+Cr. 99.51</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -7328,8 +7328,8 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>782,032
-Cr. 78.20</t>
+          <t>-213,035
+Cr. -21.30</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -7363,8 +7363,8 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>644,948
+Cr. 64.49</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -7381,30 +7381,30 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>882,061
-Cr. 88.21</t>
+          <t>911,131
+Cr. 91.11</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>318,069
-Cr. 31.81</t>
+          <t>347,139
+Cr. 34.71</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>882,061
-Cr. 88.21</t>
+          <t>266,183
+Cr. 26.62</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -7433,8 +7433,8 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>875,942
+Cr. 87.59</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -7451,25 +7451,25 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>987,240
-Cr. 98.72</t>
+          <t>995,022
+Cr. 99.50</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>128,928
-Cr. 12.89</t>
+          <t>136,710
+Cr. 13.67</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>987,240
-Cr. 98.72</t>
+          <t>119,080
+Cr. 11.91</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -7503,8 +7503,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>1,564,866
+Cr. 156.49</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -7521,30 +7521,30 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1,953,133
-Cr. 195.31</t>
+          <t>1,978,638
+Cr. 197.86</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>556,230
-Cr. 55.62</t>
+          <t>581,736
+Cr. 58.17</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>1,953,133
-Cr. 195.31</t>
+          <t>413,772
+Cr. 41.38</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -7573,8 +7573,8 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>2,029,601
+Cr. 202.96</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -7591,14 +7591,14 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2,193,589
-Cr. 219.36</t>
+          <t>2,192,865
+Cr. 219.29</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>348,270
-Cr. 34.83</t>
+          <t>347,546
+Cr. 34.75</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -7608,8 +7608,8 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2,193,589
-Cr. 219.36</t>
+          <t>163,264
+Cr. 16.33</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -7643,8 +7643,8 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>5,379,265
+Cr. 537.93</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -7661,30 +7661,30 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>4,657,805
-Cr. 465.78</t>
+          <t>5,702,475
+Cr. 570.25</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>-178,531
-Cr. -17.85</t>
+          <t>866,139
+Cr. 86.61</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>118</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>4,657,805
-Cr. 465.78</t>
+          <t>323,210
+Cr. 32.32</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -7713,8 +7713,8 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>836,072
+Cr. 83.61</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -7731,14 +7731,14 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>915,761
-Cr. 91.58</t>
+          <t>916,954
+Cr. 91.70</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>335,414
-Cr. 33.54</t>
+          <t>336,607
+Cr. 33.66</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -7748,8 +7748,8 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>915,761
-Cr. 91.58</t>
+          <t>80,882
+Cr. 8.09</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -7783,8 +7783,8 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>411,167
+Cr. 41.12</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -7801,25 +7801,25 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>439,545
-Cr. 43.95</t>
+          <t>441,761
+Cr. 44.18</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>25,112
-Cr. 2.51</t>
+          <t>27,328
+Cr. 2.73</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>439,545
-Cr. 43.95</t>
+          <t>30,594
+Cr. 3.06</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -7853,8 +7853,8 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>501,081
+Cr. 50.11</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -7871,13 +7871,13 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>532,661
+          <t>532,662
 Cr. 53.27</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>-5,284
+          <t>-5,283
 Cr. -0.53</t>
         </is>
       </c>
@@ -7888,8 +7888,8 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>532,661
-Cr. 53.27</t>
+          <t>31,581
+Cr. 3.16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -7919,8 +7919,8 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>15,141,032
+Cr. 1514.10</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -7937,30 +7937,30 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>15,417,243
-Cr. 1541.72</t>
+          <t>16,528,995
+Cr. 1652.90</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>1,835,629
-Cr. 183.56</t>
+          <t>2,947,381
+Cr. 294.74</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>15,417,243
-Cr. 1541.72</t>
+          <t>1,387,963
+Cr. 138.80</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -7989,8 +7989,8 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>0
-Cr. 0.00</t>
+          <t>1,655,141
+Cr. 165.51</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -8007,30 +8007,30 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>1,578,852
-Cr. 157.89</t>
+          <t>1,578,052
+Cr. 157.81</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>1,584,287
-Cr. 158.43</t>
+          <t>1,583,487
+Cr. 158.35</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>-29047</t>
+          <t>-29033</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>1,578,852
-Cr. 157.89</t>
+          <t>-77,089
+Cr. -7.71</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>-12103</t>
+          <t>-12097</t>
         </is>
       </c>
     </row>
